--- a/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
+++ b/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="391">
   <si>
     <t xml:space="preserve">COTIZACIÓN ETAPA 1 - VIVIENDA UNIFAMILIAR, CHORRILLOS</t>
   </si>
@@ -691,13 +691,52 @@
     <t xml:space="preserve">Alquiler vibrador</t>
   </si>
   <si>
-    <t xml:space="preserve">encof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alquiler / reposición de encofrado (tablas, puntales, fenólico)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tu Excel 2,000; +500 por VE sobre zapata</t>
+    <t xml:space="preserve">trompo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trompo (mezcladora) - compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vibc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vibradora de concreto - compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triplay fenólico film 18 mm 1.22×2.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac: S/ 85-107 por 10 o más unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad de planchas fenólicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83 m² de VE+VC a la vez, 3 piezas de 0.70×1.22 por plancha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listones, estacas, tensores y tirafondos para encofrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supuesto: ~60 listones 2"x3"x10' + accesorios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor que te queda en equipos y encofrado al terminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trompo/vibradora ~75%, fenólico tras 4-5 usos ~30%</t>
   </si>
   <si>
     <t xml:space="preserve">MATERIALES - ETAPA 1 (cantidades por despiece real de varillas)</t>
@@ -1087,13 +1126,22 @@
     <t xml:space="preserve">Confirmar si está incluido</t>
   </si>
   <si>
-    <t xml:space="preserve">Alquiler / reposición de encofrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezcladora (4 días) y vibrador (2 días)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solados, ciclópeo, sobrecimiento, solera, mortero; vibrado de premezclado</t>
+    <t xml:space="preserve">Compra trompo (mezcladora)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queda para otras obras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra vibradora de concreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra encofrado: fenólico 18 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 planchas: VE+VC (83 m²) van en un solo vaciado; luego se reusan en columnas, sobrecimiento y cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compra encofrado: listones 2"x3"x10', estacas, tensores</t>
   </si>
   <si>
     <t xml:space="preserve">SCTR + EPP (casco, botas, guantes, lentes)</t>
@@ -1111,7 +1159,7 @@
     <t xml:space="preserve">~10 semanas</t>
   </si>
   <si>
-    <t xml:space="preserve">TOTAL DE MIS COSTOS</t>
+    <t xml:space="preserve">TOTAL DE MIS COSTOS (salida de caja)</t>
   </si>
   <si>
     <t xml:space="preserve">COBRO DE MANO DE OBRA AL CLIENTE</t>
@@ -1120,16 +1168,28 @@
     <t xml:space="preserve">Hoja Mano de obra (redondeado)</t>
   </si>
   <si>
-    <t xml:space="preserve">MI GANANCIA (incluye pago por mi trabajo y dirección)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganancia por semana</t>
+    <t xml:space="preserve">MI GANANCIA EN EFECTIVO (cobro - salida de caja)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo que te queda en el bolsillo al terminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor de equipos y encofrado que te quedan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los puedes usar en la siguiente obra o vender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MI GANANCIA REAL (efectivo + equipos que te quedan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganancia real por semana</t>
   </si>
   <si>
     <t xml:space="preserve">Compárala con lo que ganarías como operario (~S/ 780/semana)</t>
   </si>
   <si>
-    <t xml:space="preserve">Margen sobre lo cobrado</t>
+    <t xml:space="preserve">Margen real sobre lo cobrado</t>
   </si>
   <si>
     <t xml:space="preserve">SENSIBILIDAD - si la obra se demora más</t>
@@ -1138,7 +1198,7 @@
     <t xml:space="preserve">Días hábiles reales</t>
   </si>
   <si>
-    <t xml:space="preserve">Mi ganancia (S/)</t>
+    <t xml:space="preserve">Mi ganancia real (S/)</t>
   </si>
 </sst>
 </file>
@@ -2791,7 +2851,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3363,13 +3423,98 @@
         <v>222</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>223</v>
+      <c r="D40" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3401,40 +3546,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -3448,7 +3593,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>49</v>
@@ -3465,7 +3610,7 @@
         <v>12800</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3473,7 +3618,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
@@ -3496,7 +3641,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>49</v>
@@ -3513,7 +3658,7 @@
         <v>3040</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3521,7 +3666,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -3538,12 +3683,12 @@
         <v>760</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -3557,7 +3702,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>148</v>
@@ -3574,7 +3719,7 @@
         <v>1687.4</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3582,7 +3727,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -3599,7 +3744,7 @@
         <v>576</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3607,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
@@ -3624,7 +3769,7 @@
         <v>175.5</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3632,7 +3777,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>49</v>
@@ -3655,7 +3800,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>49</v>
@@ -3678,7 +3823,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>49</v>
@@ -3698,7 +3843,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -3729,7 +3874,7 @@
         <v>5761.44</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3754,7 +3899,7 @@
         <v>11262.87</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3779,7 +3924,7 @@
         <v>6436.84</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3804,7 +3949,7 @@
         <v>2688.04</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3829,7 +3974,7 @@
         <v>119.4</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3837,7 +3982,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>174</v>
@@ -3854,12 +3999,12 @@
         <v>699.8</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -3873,7 +4018,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>109</v>
@@ -3890,7 +4035,7 @@
         <v>364</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3898,7 +4043,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>109</v>
@@ -3915,7 +4060,7 @@
         <v>262.5</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3923,7 +4068,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>113</v>
@@ -3940,7 +4085,7 @@
         <v>4058.4</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3948,7 +4093,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>185</v>
@@ -3965,7 +4110,7 @@
         <v>165</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3973,7 +4118,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>185</v>
@@ -3990,7 +4135,7 @@
         <v>80</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3998,7 +4143,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>113</v>
@@ -4015,7 +4160,7 @@
         <v>120</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4023,7 +4168,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>192</v>
@@ -4080,7 +4225,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4088,7 +4233,7 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -4097,16 +4242,16 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4114,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>195</v>
@@ -4131,7 +4276,7 @@
         <v>2300</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4139,7 +4284,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>199</v>
@@ -4156,7 +4301,7 @@
         <v>1040</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4181,7 +4326,7 @@
         <v>375</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4189,7 +4334,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>192</v>
@@ -4212,7 +4357,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>127</v>
@@ -4234,7 +4379,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>127</v>
@@ -4250,7 +4395,7 @@
         <v>300</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4294,12 +4439,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4313,23 +4458,23 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4397,7 +4542,7 @@
         <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
@@ -4414,13 +4559,13 @@
         <v>3564.8</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="I7" s="26" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4428,7 +4573,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>42</v>
@@ -4451,7 +4596,7 @@
         <v>3.008</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4459,7 +4604,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -4489,7 +4634,7 @@
         <v>57</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>49</v>
@@ -4513,7 +4658,7 @@
         <v>7.6375</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4521,7 +4666,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>42</v>
@@ -4551,7 +4696,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -4581,7 +4726,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
@@ -4611,7 +4756,7 @@
         <v>73</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>42</v>
@@ -4638,10 +4783,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>109</v>
@@ -4667,10 +4812,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>109</v>
@@ -4699,7 +4844,7 @@
         <v>83</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>42</v>
@@ -4722,7 +4867,7 @@
         <v>6.90833333333333</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4730,7 +4875,7 @@
         <v>86</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>42</v>
@@ -4760,7 +4905,7 @@
         <v>77</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>49</v>
@@ -4783,15 +4928,15 @@
         <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>109</v>
@@ -4814,7 +4959,7 @@
         <v>13.23</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4822,7 +4967,7 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>42</v>
@@ -4852,7 +4997,7 @@
         <v>95</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>49</v>
@@ -4875,15 +5020,15 @@
         <v>1</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>109</v>
@@ -4912,7 +5057,7 @@
         <v>104</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>42</v>
@@ -4939,10 +5084,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>49</v>
@@ -4971,7 +5116,7 @@
         <v>111</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>113</v>
@@ -5001,7 +5146,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>42</v>
@@ -5031,7 +5176,7 @@
         <v>117</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>42</v>
@@ -5091,7 +5236,7 @@
         <v>125</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>199</v>
@@ -5114,15 +5259,15 @@
         <v>1</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>127</v>
@@ -5148,7 +5293,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>127</v>
@@ -5173,7 +5318,7 @@
         <v>30357.8</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="I33" s="27" t="n">
         <f aca="false">SUM(I5:I31)</f>
@@ -5182,7 +5327,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="28" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="F34" s="29" t="n">
         <f aca="false">CEILING(F33,500)</f>
@@ -5205,7 +5350,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -5215,12 +5360,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5228,68 +5373,68 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B5" s="26" t="n">
         <f aca="false">'Mano de obra'!$I$33</f>
         <v>79.0450714285714</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="B6" s="30" t="n">
         <v>1.35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B7" s="31" t="n">
         <v>0.1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B8" s="32" t="n">
         <f aca="false">ROUNDUP(B5/B6*(1+B7),0)</f>
         <v>65</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">B8/6</f>
         <v>10.8333333333333</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5298,13 +5443,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="B12" s="32" t="n">
         <f aca="false">B8*Precios!$D$32</f>
@@ -5314,7 +5459,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">B8*Precios!$D$33</f>
@@ -5324,26 +5469,26 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B14" s="32" t="n">
         <f aca="false">6*Precios!$D$33</f>
         <v>480</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="B15" s="32" t="n">
         <f aca="false">13*Precios!$D$30</f>
         <v>1950</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5355,185 +5500,233 @@
         <v>300</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">Precios!$D$36</f>
-        <v>2500</v>
-      </c>
-      <c r="C17" s="4"/>
+        <v>1000</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B18" s="32" t="n">
-        <f aca="false">4*Precios!$D$34+2*Precios!$D$35</f>
-        <v>560</v>
+        <f aca="false">Precios!$D$37</f>
+        <v>400</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B19" s="33" t="n">
-        <v>600</v>
+        <v>369</v>
+      </c>
+      <c r="B19" s="32" t="n">
+        <f aca="false">Precios!$D$39*Precios!$D$38</f>
+        <v>3040</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B20" s="33" t="n">
-        <v>400</v>
+        <v>371</v>
+      </c>
+      <c r="B20" s="32" t="n">
+        <f aca="false">Precios!$D$40</f>
+        <v>900</v>
       </c>
       <c r="C20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="B21" s="33" t="n">
         <v>600</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="B22" s="34" t="n">
-        <f aca="false">SUM(B12:B21)</f>
-        <v>21040</v>
+      <c r="A22" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B22" s="33" t="n">
+        <v>400</v>
       </c>
       <c r="C22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4"/>
-      <c r="C23" s="4"/>
+      <c r="A23" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23" s="33" t="n">
+        <v>600</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B24" s="34" t="n">
+        <f aca="false">SUM(B12:B23)</f>
+        <v>23320</v>
+      </c>
+      <c r="C24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4"/>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B26" s="34" t="n">
         <f aca="false">'Mano de obra'!$F$34</f>
         <v>30500</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B25" s="34" t="n">
-        <f aca="false">B24-B22</f>
-        <v>9460</v>
-      </c>
-      <c r="C25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="B26" s="32" t="n">
-        <f aca="false">B25/B9</f>
-        <v>873.230769230769</v>
-      </c>
       <c r="C26" s="4" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B27" s="6" t="n">
-        <f aca="false">B25/B24</f>
-        <v>0.31016393442623</v>
-      </c>
-      <c r="C27" s="4"/>
+      <c r="A27" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B27" s="34" t="n">
+        <f aca="false">B26-B24</f>
+        <v>7180</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B28" s="32" t="n">
+        <f aca="false">(B17+B18+B19+B20)*Precios!$D$41</f>
+        <v>2403</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>273</v>
+      <c r="A29" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B29" s="34" t="n">
+        <f aca="false">B27+B28</f>
+        <v>9583</v>
+      </c>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B30" s="32" t="n">
+        <f aca="false">B29/B9</f>
+        <v>884.584615384615</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="n">
-        <v>50</v>
-      </c>
-      <c r="B31" s="32" t="n">
-        <f aca="false">B24-(B22-B12-B13+50*(Precios!$D$32+Precios!$D$33))</f>
-        <v>12610</v>
+      <c r="A31" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <f aca="false">B29/B26</f>
+        <v>0.314196721311475</v>
       </c>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="B32" s="32" t="n">
-        <f aca="false">B24-(B22-B12-B13+60*(Precios!$D$32+Precios!$D$33))</f>
-        <v>10510</v>
-      </c>
-      <c r="C32" s="4"/>
-    </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="n">
-        <v>70</v>
-      </c>
-      <c r="B33" s="32" t="n">
-        <f aca="false">B24-(B22-B12-B13+70*(Precios!$D$32+Precios!$D$33))</f>
-        <v>8410</v>
-      </c>
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="n">
-        <v>80</v>
-      </c>
-      <c r="B34" s="32" t="n">
-        <f aca="false">B24-(B22-B12-B13+80*(Precios!$D$32+Precios!$D$33))</f>
-        <v>6310</v>
-      </c>
-      <c r="C34" s="4"/>
+      <c r="A33" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="n">
+        <v>50</v>
+      </c>
+      <c r="B35" s="32" t="n">
+        <f aca="false">B29-(50-B8)*(Precios!$D$32+Precios!$D$33)</f>
+        <v>12733</v>
+      </c>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="n">
+        <v>60</v>
+      </c>
+      <c r="B36" s="32" t="n">
+        <f aca="false">B29-(60-B8)*(Precios!$D$32+Precios!$D$33)</f>
+        <v>10633</v>
+      </c>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="n">
+        <v>70</v>
+      </c>
+      <c r="B37" s="32" t="n">
+        <f aca="false">B29-(70-B8)*(Precios!$D$32+Precios!$D$33)</f>
+        <v>8533</v>
+      </c>
+      <c r="C37" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="B38" s="32" t="n">
+        <f aca="false">B29-(80-B8)*(Precios!$D$32+Precios!$D$33)</f>
+        <v>6433</v>
+      </c>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="B35" s="32" t="n">
-        <f aca="false">B24-(B22-B12-B13+90*(Precios!$D$32+Precios!$D$33))</f>
-        <v>4210</v>
-      </c>
-      <c r="C35" s="4"/>
+      <c r="B39" s="32" t="n">
+        <f aca="false">B29-(90-B8)*(Precios!$D$32+Precios!$D$33)</f>
+        <v>4333</v>
+      </c>
+      <c r="C39" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
+++ b/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
@@ -382,10 +382,10 @@
     <t xml:space="preserve">05.02</t>
   </si>
   <si>
-    <t xml:space="preserve">Muro perímetro vivienda hasta +2.00 (con junta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7 m × 1.80</t>
+    <t xml:space="preserve">Muro perímetro vivienda hasta +2.30 (altura final del 1er nivel, con junta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7 m × 2.10 (de +0.20 a +2.30, fondo de viga). E-10 paraba en +2.00</t>
   </si>
   <si>
     <t xml:space="preserve">05.03</t>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">ml</t>
   </si>
   <si>
-    <t xml:space="preserve">Juntas muro-columna × 1.80 + cerco</t>
+    <t xml:space="preserve">E-10 42.0 + 20 juntas muro-columna × 0.30 adicionales</t>
   </si>
   <si>
     <t xml:space="preserve">06  VARIOS</t>
@@ -793,7 +793,7 @@
     <t xml:space="preserve">Cemento (solado, ciclópeo, sobrecimiento, solera, mortero)</t>
   </si>
   <si>
-    <t xml:space="preserve">Solado 17 + ciclópeo 7 + sobrecim. 11 + solera 4 + mortero 20</t>
+    <t xml:space="preserve">Solado 17 + ciclópeo 7 + sobrecim. 11 + solera 4 + mortero 22</t>
   </si>
   <si>
     <t xml:space="preserve">Hormigón (solado, ciclópeo, sobrecimiento)</t>
@@ -805,7 +805,7 @@
     <t xml:space="preserve">Arena gruesa (solera + mortero de muros)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2 + 87 m² × 0.028</t>
+    <t xml:space="preserve">0.2 + 96.6 m² × 0.028</t>
   </si>
   <si>
     <t xml:space="preserve">Piedra chancada 1/2" (solera)</t>
@@ -859,7 +859,7 @@
     <t xml:space="preserve">Ladrillo KK 18 huecos (+5%)</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9 m² × 39 × 1.05</t>
+    <t xml:space="preserve">96.6 m² × 39 × 1.05</t>
   </si>
   <si>
     <t xml:space="preserve">Tecnopor 4" bajo VE</t>
@@ -871,7 +871,7 @@
     <t xml:space="preserve">Tecnopor 1" para juntas</t>
   </si>
   <si>
-    <t xml:space="preserve">12 m² ÷ 2.88</t>
+    <t xml:space="preserve">≈ 13.5 m² ÷ 2.88</t>
   </si>
   <si>
     <t xml:space="preserve">Epóxico para anclajes</t>
@@ -1826,11 +1826,11 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Materiales!$F$32</f>
-        <v>52798.19</v>
+        <v>53330.89</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">B5/$B$10</f>
-        <v>0.580909432680188</v>
+        <v>0.580010255667419</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C6" s="6" t="n">
         <f aca="false">B6/$B$10</f>
-        <v>0.051876550599312</v>
+        <v>0.051278880878828</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>9</v>
@@ -1858,11 +1858,11 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">'Mano de obra'!$F$34</f>
-        <v>30500</v>
+        <v>31000</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">B7/$B$10</f>
-        <v>0.335574717556525</v>
+        <v>0.337146406626441</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
@@ -1874,11 +1874,11 @@
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">SUM(B5:B7)</f>
-        <v>88013.19</v>
+        <v>89045.89</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">B8/$B$10</f>
-        <v>0.968360700836025</v>
+        <v>0.968435543172688</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,11 +1887,11 @@
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">0.05*(B5+B6)</f>
-        <v>2875.6595</v>
+        <v>2902.2945</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">B9/$B$10</f>
-        <v>0.031639299163975</v>
+        <v>0.0315644568273123</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>14</v>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">B8+B9</f>
-        <v>90888.8495</v>
+        <v>91948.1845</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">B10/$B$10</f>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">$B$7*C15</f>
-        <v>4575</v>
+        <v>4650</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>0.15</v>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B16" s="5" t="n">
         <f aca="false">$B$7*C16</f>
-        <v>9150</v>
+        <v>9300</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>0.3</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="B17" s="5" t="n">
         <f aca="false">$B$7*C17</f>
-        <v>3660</v>
+        <v>3720</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>0.12</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">$B$7*C18</f>
-        <v>7015</v>
+        <v>7130</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>0.23</v>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">$B$7*C19</f>
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>0.2</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">SUM(B15:B19)</f>
-        <v>30500</v>
+        <v>31000</v>
       </c>
       <c r="C20" s="11" t="n">
         <f aca="false">SUM(C15:C19)</f>
@@ -2718,50 +2718,50 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="19" t="n">
         <v>57.1</v>
       </c>
-      <c r="E34" s="15" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="F34" s="16" t="n">
+      <c r="E34" s="20" t="n">
+        <v>66.6</v>
+      </c>
+      <c r="F34" s="21" t="n">
         <f aca="false">E34-D34</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="17" t="s">
+        <v>9.49999999999999</v>
+      </c>
+      <c r="G34" s="22" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="E35" s="15" t="n">
-        <v>42</v>
-      </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="F35" s="21" t="n">
         <f aca="false">E35-D35</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="22" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
         <v>148</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">Precios!$D$7</f>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">D11*E11</f>
-        <v>1687.4</v>
+        <v>1744.6</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>255</v>
@@ -3758,7 +3758,7 @@
         <v>49</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">Precios!$D$8</f>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="F13" s="5" t="n">
         <f aca="false">D13*E13</f>
-        <v>175.5</v>
+        <v>195</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>259</v>
@@ -4074,7 +4074,7 @@
         <v>113</v>
       </c>
       <c r="D27" s="24" t="n">
-        <v>3560</v>
+        <v>3960</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">Precios!$D$21</f>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="F27" s="5" t="n">
         <f aca="false">D27*E27</f>
-        <v>4058.4</v>
+        <v>4514.4</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>277</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="F32" s="8" t="n">
         <f aca="false">SUM(F5:F31)</f>
-        <v>52798.19</v>
+        <v>53330.89</v>
       </c>
     </row>
   </sheetData>
@@ -5183,21 +5183,21 @@
       </c>
       <c r="D28" s="5" t="n">
         <f aca="false">Metrados!$E$34</f>
-        <v>57.1</v>
+        <v>66.6</v>
       </c>
       <c r="E28" s="15" t="n">
         <v>35</v>
       </c>
       <c r="F28" s="5" t="n">
         <f aca="false">D28*E28</f>
-        <v>1998.5</v>
+        <v>2331</v>
       </c>
       <c r="H28" s="24" t="n">
         <v>10</v>
       </c>
       <c r="I28" s="26" t="n">
         <f aca="false">D28/H28</f>
-        <v>5.71</v>
+        <v>6.66</v>
       </c>
       <c r="J28" s="4"/>
     </row>
@@ -5213,21 +5213,21 @@
       </c>
       <c r="D29" s="5" t="n">
         <f aca="false">Metrados!$E$35</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E29" s="15" t="n">
         <v>8</v>
       </c>
       <c r="F29" s="5" t="n">
         <f aca="false">D29*E29</f>
-        <v>336</v>
+        <v>384</v>
       </c>
       <c r="H29" s="24" t="n">
         <v>60</v>
       </c>
       <c r="I29" s="26" t="n">
         <f aca="false">D29/H29</f>
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J29" s="4"/>
     </row>
@@ -5315,14 +5315,14 @@
       </c>
       <c r="F33" s="8" t="n">
         <f aca="false">SUM(F5:F32)</f>
-        <v>30357.8</v>
+        <v>30738.3</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>342</v>
       </c>
       <c r="I33" s="27" t="n">
         <f aca="false">SUM(I5:I31)</f>
-        <v>79.0450714285714</v>
+        <v>80.0950714285714</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F34" s="29" t="n">
         <f aca="false">CEILING(F33,500)</f>
-        <v>30500</v>
+        <v>31000</v>
       </c>
     </row>
   </sheetData>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="B5" s="26" t="n">
         <f aca="false">'Mano de obra'!$I$33</f>
-        <v>79.0450714285714</v>
+        <v>80.0950714285714</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>349</v>
@@ -5419,7 +5419,7 @@
       </c>
       <c r="B8" s="32" t="n">
         <f aca="false">ROUNDUP(B5/B6*(1+B7),0)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>355</v>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B9" s="26" t="n">
         <f aca="false">B8/6</f>
-        <v>10.8333333333333</v>
+        <v>11</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>357</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="B12" s="32" t="n">
         <f aca="false">B8*Precios!$D$32</f>
-        <v>8450</v>
+        <v>8580</v>
       </c>
       <c r="C12" s="4"/>
     </row>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="B13" s="32" t="n">
         <f aca="false">B8*Precios!$D$33</f>
-        <v>5200</v>
+        <v>5280</v>
       </c>
       <c r="C13" s="4"/>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B24" s="34" t="n">
         <f aca="false">SUM(B12:B23)</f>
-        <v>23320</v>
+        <v>23530</v>
       </c>
       <c r="C24" s="4"/>
     </row>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="B26" s="34" t="n">
         <f aca="false">'Mano de obra'!$F$34</f>
-        <v>30500</v>
+        <v>31000</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>379</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="B27" s="34" t="n">
         <f aca="false">B26-B24</f>
-        <v>7180</v>
+        <v>7470</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>381</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="B29" s="34" t="n">
         <f aca="false">B27+B28</f>
-        <v>9583</v>
+        <v>9873</v>
       </c>
       <c r="C29" s="4"/>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B30" s="32" t="n">
         <f aca="false">B29/B9</f>
-        <v>884.584615384615</v>
+        <v>897.545454545455</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>386</v>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B31" s="6" t="n">
         <f aca="false">B29/B26</f>
-        <v>0.314196721311475</v>
+        <v>0.318483870967742</v>
       </c>
       <c r="C31" s="4"/>
     </row>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B35" s="32" t="n">
         <f aca="false">B29-(50-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>12733</v>
+        <v>13233</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="B36" s="32" t="n">
         <f aca="false">B29-(60-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>10633</v>
+        <v>11133</v>
       </c>
       <c r="C36" s="4"/>
     </row>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B37" s="32" t="n">
         <f aca="false">B29-(70-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>8533</v>
+        <v>9033</v>
       </c>
       <c r="C37" s="4"/>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="B38" s="32" t="n">
         <f aca="false">B29-(80-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>6433</v>
+        <v>6933</v>
       </c>
       <c r="C38" s="4"/>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B39" s="32" t="n">
         <f aca="false">B29-(90-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>4333</v>
+        <v>4833</v>
       </c>
       <c r="C39" s="4"/>
     </row>

--- a/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
+++ b/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="395">
   <si>
     <t xml:space="preserve">COTIZACIÓN ETAPA 1 - VIVIENDA UNIFAMILIAR, CHORRILLOS</t>
   </si>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">Relleno compactado con material propio hasta -0.20</t>
   </si>
   <si>
-    <t xml:space="preserve">Vivienda: 111.4 excav. - 43.1 enterrado - 14.5 (capa superior 0.20) = 53.8; cerco 7.3. E-10 79.4 NO CABE en la excavación</t>
+    <t xml:space="preserve">Vivienda: 111.4 excav. - 44.9 enterrado (incl. sobrecimiento bajo -0.20) - 14.5 (capa superior 0.20) = 52.0; cerco 7.3. E-10 79.4 NO CABE en la excavación</t>
   </si>
   <si>
     <t xml:space="preserve">02.05</t>
@@ -214,7 +214,7 @@
     <t xml:space="preserve">Eliminación de material excedente (esponj. 25%)</t>
   </si>
   <si>
-    <t xml:space="preserve">(124.7 - 61.1) × 1.25. E-10 sale bajo porque su relleno está inflado</t>
+    <t xml:space="preserve">(124.7 - 59.3) × 1.25. E-10 sale bajo porque su relleno está inflado</t>
   </si>
   <si>
     <t xml:space="preserve">03  CONCRETO SIMPLE</t>
@@ -241,10 +241,10 @@
     <t xml:space="preserve">03.03</t>
   </si>
   <si>
-    <t xml:space="preserve">Sobrecimiento 1:8 + 25% PM 0.15×0.40 (perímetro + cerco)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(31.7 + 11.8) × 0.15 × 0.40</t>
+    <t xml:space="preserve">Sobrecimiento 1:8 + 25% PM 0.15 de ancho (perímetro + cerco)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debe arrancar desde la viga, no desde -0.20: sobre VE (top -0.30) h = 0.50 → 20.98 m; sobre VC de ejes A y C (top -1.10) h ≈ 1.25 → 10.72 m; cerco h = 0.40 → 11.78 m</t>
   </si>
   <si>
     <t xml:space="preserve">03.04</t>
@@ -253,7 +253,7 @@
     <t xml:space="preserve">Encofrado de sobrecimiento (2 caras)</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5 × 0.40 × 2</t>
+    <t xml:space="preserve">2 × (0.50 × 20.98 + 1.25 × 10.72 + 0.40 × 11.78)</t>
   </si>
   <si>
     <t xml:space="preserve">04  CONCRETO ARMADO f'c 210</t>
@@ -265,7 +265,7 @@
     <t xml:space="preserve">Zapatas Z-1 a Z-5 (vaciado contra terreno)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuadro E-01</t>
+    <t xml:space="preserve">Cuadro E-01. OJO: la excavación lleva 0.10 de sobreancho; si se vacía contra terreno, ese hueco se llena de concreto (+3.8 m³). Perfilar a la medida exacta los 0.50 inferiores</t>
   </si>
   <si>
     <t xml:space="preserve">04.02</t>
@@ -430,6 +430,9 @@
     <t xml:space="preserve">Acero de columnas 1er piso: 2,646 kg (E-10) verificado (barras Ø5/8" de 6.00 m de arranque + estribos Ø1/2" 1,342 kg + montaje 3/8" 38 kg).</t>
   </si>
   <si>
+    <t xml:space="preserve">Diferencias menores a favor (no se cambian): zanjas de VE medidas sin descontar el sobreancho de los pozos (~2.5 m³ de más); encofrado de columnas sin descontar las caras donde llega la VE (~6.7 m²).</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRECIOS DE MATERIALES Y SERVICIOS - Lima, octubre 2026 (con IGV)</t>
   </si>
   <si>
@@ -769,7 +772,7 @@
     <t xml:space="preserve">Premezclado f'c 210 - vaciado 1: zapatas + VE + VC + ZC + VA cerco</t>
   </si>
   <si>
-    <t xml:space="preserve">(23.39 + 11.65 + 0.66 + 1.36 + 1.18) × 1.04 = 39.8 → pedir 40.0</t>
+    <t xml:space="preserve">(23.39 + 11.65 + 0.66 + 1.36 + 1.18) × 1.04 = 39.8 + 2.0 por sobreexcavación de la retro → 42.0</t>
   </si>
   <si>
     <t xml:space="preserve">Bomba - vaciado 1</t>
@@ -793,13 +796,13 @@
     <t xml:space="preserve">Cemento (solado, ciclópeo, sobrecimiento, solera, mortero)</t>
   </si>
   <si>
-    <t xml:space="preserve">Solado 17 + ciclópeo 7 + sobrecim. 11 + solera 4 + mortero 22</t>
+    <t xml:space="preserve">Solado 17 + ciclópeo 7 + sobrecim. 17 + solera 4 + mortero 22</t>
   </si>
   <si>
     <t xml:space="preserve">Hormigón (solado, ciclópeo, sobrecimiento)</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4 + 1.9 + 2.3</t>
+    <t xml:space="preserve">5.4 + 1.9 + 3.7</t>
   </si>
   <si>
     <t xml:space="preserve">Arena gruesa (solera + mortero de muros)</t>
@@ -847,13 +850,13 @@
     <t xml:space="preserve">Alambre N°8 (encofrado)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25 kg/m² × 224 m²</t>
+    <t xml:space="preserve">0.25 kg/m² × 246 m²</t>
   </si>
   <si>
     <t xml:space="preserve">Clavos</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15 kg/m² × 224 m²</t>
+    <t xml:space="preserve">0.15 kg/m² × 246 m²</t>
   </si>
   <si>
     <t xml:space="preserve">Ladrillo KK 18 huecos (+5%)</t>
@@ -892,13 +895,13 @@
     <t xml:space="preserve">Eliminación de desmonte - volquete 18 m³</t>
   </si>
   <si>
-    <t xml:space="preserve">79.5 m³ suelto ÷ 18</t>
+    <t xml:space="preserve">81.7 m³ suelto ÷ 18</t>
   </si>
   <si>
     <t xml:space="preserve">Alquiler de apisonador para relleno</t>
   </si>
   <si>
-    <t xml:space="preserve">61 m³ ÷ 8 m³/día</t>
+    <t xml:space="preserve">59 m³ ÷ 8 m³/día</t>
   </si>
   <si>
     <t xml:space="preserve">1 por vaciado</t>
@@ -922,6 +925,12 @@
     <t xml:space="preserve">Precio por partida (destajo Lima). La excavación incluye la retroexcavadora y el carguío. Columnas H-J: uso interno (rendimiento de tu cuadrilla operario + ayudante).</t>
   </si>
   <si>
+    <t xml:space="preserve">Precio objetivo MO (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Metrado</t>
   </si>
   <si>
@@ -934,6 +943,9 @@
     <t xml:space="preserve">Días-cuadrilla</t>
   </si>
   <si>
+    <t xml:space="preserve">P.U. base (S/)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Excavación con retroexcavadora (zapatas + zanjas) y carguío</t>
   </si>
   <si>
@@ -991,7 +1003,7 @@
     <t xml:space="preserve">Colocación de tecnopor bajo VE</t>
   </si>
   <si>
-    <t xml:space="preserve">Vaciado y vibrado premezclado - cimentación (40 m³)</t>
+    <t xml:space="preserve">Vaciado y vibrado premezclado - cimentación (42 m³)</t>
   </si>
   <si>
     <t xml:space="preserve">1 día + eventuales</t>
@@ -1051,7 +1063,7 @@
     <t xml:space="preserve">Limpieza final</t>
   </si>
   <si>
-    <t xml:space="preserve">Dirección técnica y residencia de obra (tú)</t>
+    <t xml:space="preserve">Dirección técnica y residencia de obra</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -1205,7 +1217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -1213,9 +1225,10 @@
     <numFmt numFmtId="168" formatCode="\+#,##0.00;\-#,##0.00;\-"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
     <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="#,##0"/>
-    <numFmt numFmtId="173" formatCode="0.00"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="173" formatCode="#,##0"/>
+    <numFmt numFmtId="174" formatCode="0.00"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1394,7 +1407,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1499,11 +1512,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1511,7 +1532,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1519,19 +1552,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1826,11 +1847,11 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">Materiales!$F$32</f>
-        <v>53330.89</v>
+        <v>54431.49</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">B5/$B$10</f>
-        <v>0.580010255667419</v>
+        <v>0.554835612431767</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
@@ -1846,7 +1867,7 @@
       </c>
       <c r="C6" s="6" t="n">
         <f aca="false">B6/$B$10</f>
-        <v>0.051278880878828</v>
+        <v>0.048061332008655</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>9</v>
@@ -1858,11 +1879,11 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">'Mano de obra'!$F$34</f>
-        <v>31000</v>
+        <v>36000</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">B7/$B$10</f>
-        <v>0.337146406626441</v>
+        <v>0.366958208337557</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
@@ -1874,11 +1895,11 @@
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">SUM(B5:B7)</f>
-        <v>89045.89</v>
+        <v>95146.49</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">B8/$B$10</f>
-        <v>0.968435543172688</v>
+        <v>0.969855152777979</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1887,11 +1908,11 @@
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">0.05*(B5+B6)</f>
-        <v>2902.2945</v>
+        <v>2957.3245</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">B9/$B$10</f>
-        <v>0.0315644568273123</v>
+        <v>0.0301448472220211</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>14</v>
@@ -1903,7 +1924,7 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">B8+B9</f>
-        <v>91948.1845</v>
+        <v>98103.8145</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">B10/$B$10</f>
@@ -1941,7 +1962,7 @@
       </c>
       <c r="B15" s="5" t="n">
         <f aca="false">$B$7*C15</f>
-        <v>4650</v>
+        <v>5400</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>0.15</v>
@@ -1953,7 +1974,7 @@
       </c>
       <c r="B16" s="5" t="n">
         <f aca="false">$B$7*C16</f>
-        <v>9300</v>
+        <v>10800</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>0.3</v>
@@ -1965,7 +1986,7 @@
       </c>
       <c r="B17" s="5" t="n">
         <f aca="false">$B$7*C17</f>
-        <v>3720</v>
+        <v>4320</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>0.12</v>
@@ -1977,7 +1998,7 @@
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">$B$7*C18</f>
-        <v>7130</v>
+        <v>8280</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>0.23</v>
@@ -1989,7 +2010,7 @@
       </c>
       <c r="B19" s="5" t="n">
         <f aca="false">$B$7*C19</f>
-        <v>6200</v>
+        <v>7200</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>0.2</v>
@@ -2001,7 +2022,7 @@
       </c>
       <c r="B20" s="8" t="n">
         <f aca="false">SUM(B15:B19)</f>
-        <v>31000</v>
+        <v>36000</v>
       </c>
       <c r="C20" s="11" t="n">
         <f aca="false">SUM(C15:C19)</f>
@@ -2044,7 +2065,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -2244,11 +2265,11 @@
         <v>79.4</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>61.1</v>
+        <v>59.3</v>
       </c>
       <c r="F12" s="21" t="n">
         <f aca="false">E12-D12</f>
-        <v>-18.3</v>
+        <v>-20.1</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>59</v>
@@ -2268,11 +2289,11 @@
         <v>53.5</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>79.5</v>
+        <v>81.7</v>
       </c>
       <c r="F13" s="21" t="n">
         <f aca="false">E13-D13</f>
-        <v>26</v>
+        <v>28.2</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>62</v>
@@ -2337,51 +2358,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="19" t="n">
         <v>2.7</v>
       </c>
-      <c r="E17" s="15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="20" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F17" s="21" t="n">
         <f aca="false">E17-D17</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="17" t="s">
+        <v>1.59</v>
+      </c>
+      <c r="G17" s="22" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="19" t="n">
         <v>35.4</v>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="20" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F18" s="21" t="n">
         <f aca="false">E18-D18</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="17" t="s">
+        <v>21.8</v>
+      </c>
+      <c r="G18" s="22" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2396,7 +2417,7 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
         <v>77</v>
       </c>
@@ -2833,6 +2854,11 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="23" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2863,37 +2889,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>49</v>
@@ -2902,15 +2928,15 @@
         <v>320</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>49</v>
@@ -2919,32 +2945,32 @@
         <v>38</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>28.6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>49</v>
@@ -2953,15 +2979,15 @@
         <v>65</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -2970,15 +2996,15 @@
         <v>80</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>49</v>
@@ -2987,15 +3013,15 @@
         <v>60</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>49</v>
@@ -3004,15 +3030,15 @@
         <v>50</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -3021,117 +3047,117 @@
         <v>50</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>80.02</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>54.41</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>35.96</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>20.06</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>7.96</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>349.9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>109</v>
@@ -3140,15 +3166,15 @@
         <v>6.5</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>109</v>
@@ -3157,15 +3183,15 @@
         <v>7.5</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>113</v>
@@ -3174,49 +3200,49 @@
         <v>1.14</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D22" s="15" t="n">
         <v>55</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>185</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>16</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>113</v>
@@ -3225,66 +3251,66 @@
         <v>120</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D25" s="15" t="n">
         <v>45</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D26" s="15" t="n">
         <v>460</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D27" s="15" t="n">
         <v>130</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>130</v>
@@ -3293,49 +3319,49 @@
         <v>75</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D29" s="15" t="n">
         <v>20</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D30" s="15" t="n">
         <v>150</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>127</v>
@@ -3344,83 +3370,83 @@
         <v>300</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D32" s="15" t="n">
         <v>130</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D33" s="15" t="n">
         <v>80</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D34" s="15" t="n">
         <v>100</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D35" s="15" t="n">
         <v>80</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>113</v>
@@ -3429,15 +3455,15 @@
         <v>1000</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>113</v>
@@ -3446,32 +3472,32 @@
         <v>400</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D38" s="15" t="n">
         <v>95</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>113</v>
@@ -3480,15 +3506,15 @@
         <v>32</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>127</v>
@@ -3497,15 +3523,15 @@
         <v>900</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>4</v>
@@ -3514,7 +3540,7 @@
         <v>0.45</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3546,40 +3572,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -3593,13 +3619,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">Precios!$D$5</f>
@@ -3607,10 +3633,10 @@
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
-        <v>12800</v>
+        <v>13440</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3618,13 +3644,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">Precios!$D$6</f>
@@ -3632,7 +3658,7 @@
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">D7*E7</f>
-        <v>1520</v>
+        <v>1596</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -3641,7 +3667,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>49</v>
@@ -3658,7 +3684,7 @@
         <v>3040</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3666,7 +3692,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -3683,12 +3709,12 @@
         <v>760</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -3702,13 +3728,13 @@
         <v>5</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">Precios!$D$7</f>
@@ -3716,10 +3742,10 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">D11*E11</f>
-        <v>1744.6</v>
+        <v>1916.2</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3727,13 +3753,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">Precios!$D$10</f>
@@ -3741,10 +3767,10 @@
       </c>
       <c r="F12" s="5" t="n">
         <f aca="false">D12*E12</f>
-        <v>576</v>
+        <v>660</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3752,7 +3778,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
@@ -3769,7 +3795,7 @@
         <v>195</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3777,7 +3803,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>49</v>
@@ -3800,7 +3826,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>49</v>
@@ -3823,13 +3849,13 @@
         <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">Precios!$D$12</f>
@@ -3837,13 +3863,13 @@
       </c>
       <c r="F16" s="5" t="n">
         <f aca="false">D16*E16</f>
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -3857,10 +3883,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>72</v>
@@ -3874,7 +3900,7 @@
         <v>5761.44</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3882,10 +3908,10 @@
         <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>207</v>
@@ -3899,7 +3925,7 @@
         <v>11262.87</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3907,10 +3933,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>179</v>
@@ -3924,7 +3950,7 @@
         <v>6436.84</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3932,10 +3958,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>134</v>
@@ -3949,7 +3975,7 @@
         <v>2688.04</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3957,10 +3983,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>15</v>
@@ -3974,7 +4000,7 @@
         <v>119.4</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3982,10 +4008,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>2</v>
@@ -3999,12 +4025,12 @@
         <v>699.8</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -4018,13 +4044,13 @@
         <v>17</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">Precios!$D$19</f>
@@ -4032,10 +4058,10 @@
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">D25*E25</f>
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4043,13 +4069,13 @@
         <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D26" s="24" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">Precios!$D$20</f>
@@ -4057,10 +4083,10 @@
       </c>
       <c r="F26" s="5" t="n">
         <f aca="false">D26*E26</f>
-        <v>262.5</v>
+        <v>277.5</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,7 +4094,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>113</v>
@@ -4085,7 +4111,7 @@
         <v>4514.4</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4093,10 +4119,10 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D28" s="24" t="n">
         <v>3</v>
@@ -4110,7 +4136,7 @@
         <v>165</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4118,10 +4144,10 @@
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D29" s="24" t="n">
         <v>5</v>
@@ -4135,7 +4161,7 @@
         <v>80</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4143,7 +4169,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>113</v>
@@ -4160,7 +4186,7 @@
         <v>120</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4168,13 +4194,13 @@
         <v>23</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D31" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">Precios!$D$25</f>
@@ -4182,7 +4208,7 @@
       </c>
       <c r="F31" s="5" t="n">
         <f aca="false">D31*E31</f>
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="G31" s="4"/>
     </row>
@@ -4192,7 +4218,7 @@
       </c>
       <c r="F32" s="8" t="n">
         <f aca="false">SUM(F5:F31)</f>
-        <v>53330.89</v>
+        <v>54431.49</v>
       </c>
     </row>
   </sheetData>
@@ -4225,7 +4251,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4233,7 +4259,7 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -4242,16 +4268,16 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4259,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>5</v>
@@ -4276,7 +4302,7 @@
         <v>2300</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4284,10 +4310,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>8</v>
@@ -4301,7 +4327,7 @@
         <v>1040</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4326,7 +4352,7 @@
         <v>375</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4334,10 +4360,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>20</v>
@@ -4357,7 +4383,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>127</v>
@@ -4379,7 +4405,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>127</v>
@@ -4395,7 +4421,7 @@
         <v>300</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4423,7 +4449,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -4435,16 +4461,36 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M3" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="N3" s="26" t="n">
+        <v>36000</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="P3" s="27" t="n">
+        <f aca="false">N3/SUMPRODUCT(D5:D32,K5:K32)</f>
+        <v>1.14815322742683</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4458,23 +4504,26 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4491,21 +4540,25 @@
         <f aca="false">Metrados!$E$6</f>
         <v>170</v>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>2</v>
+      <c r="E5" s="5" t="n">
+        <f aca="false">ROUND(K5*$P$3,2)</f>
+        <v>2.3</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">D5*E5</f>
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>170</v>
       </c>
-      <c r="I5" s="26" t="n">
+      <c r="I5" s="28" t="n">
         <f aca="false">D5/H5</f>
         <v>1</v>
       </c>
       <c r="J5" s="4"/>
+      <c r="K5" s="15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -4521,28 +4574,32 @@
         <f aca="false">Metrados!$E$7</f>
         <v>170</v>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>3</v>
+      <c r="E6" s="5" t="n">
+        <f aca="false">ROUND(K6*$P$3,2)</f>
+        <v>3.44</v>
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
-        <v>510</v>
+        <v>584.8</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>170</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="28" t="n">
         <f aca="false">D6/H6</f>
         <v>1</v>
       </c>
       <c r="J6" s="4"/>
+      <c r="K6" s="15" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
@@ -4551,21 +4608,25 @@
         <f aca="false">Metrados!$E$9+Metrados!$E$10</f>
         <v>111.4</v>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>32</v>
+      <c r="E7" s="5" t="n">
+        <f aca="false">ROUND(K7*$P$3,2)</f>
+        <v>36.74</v>
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">D7*E7</f>
-        <v>3564.8</v>
+        <v>4092.836</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="I7" s="26" t="n">
+        <v>307</v>
+      </c>
+      <c r="I7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4573,7 +4634,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>42</v>
@@ -4581,22 +4642,26 @@
       <c r="D8" s="15" t="n">
         <v>75.2</v>
       </c>
-      <c r="E8" s="15" t="n">
-        <v>6</v>
+      <c r="E8" s="5" t="n">
+        <f aca="false">ROUND(K8*$P$3,2)</f>
+        <v>6.89</v>
       </c>
       <c r="F8" s="5" t="n">
         <f aca="false">D8*E8</f>
-        <v>451.2</v>
+        <v>518.128</v>
       </c>
       <c r="H8" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="28" t="n">
         <f aca="false">D8/H8</f>
         <v>3.008</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4604,7 +4669,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -4613,52 +4678,60 @@
         <f aca="false">Metrados!$E$11</f>
         <v>13.3</v>
       </c>
-      <c r="E9" s="15" t="n">
-        <v>45</v>
+      <c r="E9" s="5" t="n">
+        <f aca="false">ROUND(K9*$P$3,2)</f>
+        <v>51.67</v>
       </c>
       <c r="F9" s="5" t="n">
         <f aca="false">D9*E9</f>
-        <v>598.5</v>
+        <v>687.211</v>
       </c>
       <c r="H9" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="26" t="n">
+      <c r="I9" s="28" t="n">
         <f aca="false">D9/H9</f>
         <v>3.325</v>
       </c>
       <c r="J9" s="4"/>
+      <c r="K9" s="15" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">Metrados!$E$12</f>
-        <v>61.1</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>30</v>
+        <v>59.3</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <f aca="false">ROUND(K10*$P$3,2)</f>
+        <v>34.44</v>
       </c>
       <c r="F10" s="5" t="n">
         <f aca="false">D10*E10</f>
-        <v>1833</v>
+        <v>2042.292</v>
       </c>
       <c r="H10" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="26" t="n">
+      <c r="I10" s="28" t="n">
         <f aca="false">D10/H10</f>
-        <v>7.6375</v>
+        <v>7.4125</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4666,7 +4739,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>42</v>
@@ -4675,28 +4748,32 @@
         <f aca="false">Metrados!$E$15</f>
         <v>50</v>
       </c>
-      <c r="E11" s="15" t="n">
-        <v>15</v>
+      <c r="E11" s="5" t="n">
+        <f aca="false">ROUND(K11*$P$3,2)</f>
+        <v>17.22</v>
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">D11*E11</f>
-        <v>750</v>
+        <v>861</v>
       </c>
       <c r="H11" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="I11" s="26" t="n">
+      <c r="I11" s="28" t="n">
         <f aca="false">D11/H11</f>
         <v>1.42857142857143</v>
       </c>
       <c r="J11" s="4"/>
+      <c r="K11" s="15" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -4705,88 +4782,100 @@
         <f aca="false">Metrados!$E$16</f>
         <v>2.2</v>
       </c>
-      <c r="E12" s="15" t="n">
-        <v>90</v>
+      <c r="E12" s="5" t="n">
+        <f aca="false">ROUND(K12*$P$3,2)</f>
+        <v>103.33</v>
       </c>
       <c r="F12" s="5" t="n">
         <f aca="false">D12*E12</f>
-        <v>198</v>
+        <v>227.326</v>
       </c>
       <c r="H12" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="28" t="n">
         <f aca="false">D12/H12</f>
         <v>0.55</v>
       </c>
       <c r="J12" s="4"/>
+      <c r="K12" s="15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="5" t="n">
         <f aca="false">Metrados!$E$17</f>
-        <v>2.7</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>120</v>
+        <v>4.29</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <f aca="false">ROUND(K13*$P$3,2)</f>
+        <v>137.78</v>
       </c>
       <c r="F13" s="5" t="n">
         <f aca="false">D13*E13</f>
-        <v>324</v>
+        <v>591.0762</v>
       </c>
       <c r="H13" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="28" t="n">
         <f aca="false">D13/H13</f>
-        <v>0.9</v>
+        <v>1.43</v>
       </c>
       <c r="J13" s="4"/>
+      <c r="K13" s="15" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D14" s="5" t="n">
         <f aca="false">Metrados!$E$18</f>
-        <v>35.4</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>22</v>
+        <v>57.2</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <f aca="false">ROUND(K14*$P$3,2)</f>
+        <v>25.26</v>
       </c>
       <c r="F14" s="5" t="n">
         <f aca="false">D14*E14</f>
-        <v>778.8</v>
+        <v>1444.872</v>
       </c>
       <c r="H14" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="I14" s="26" t="n">
+      <c r="I14" s="28" t="n">
         <f aca="false">D14/H14</f>
-        <v>2.52857142857143</v>
+        <v>4.08571428571429</v>
       </c>
       <c r="J14" s="4"/>
+      <c r="K14" s="15" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>109</v>
@@ -4794,28 +4883,32 @@
       <c r="D15" s="15" t="n">
         <v>823</v>
       </c>
-      <c r="E15" s="15" t="n">
-        <v>1.1</v>
+      <c r="E15" s="5" t="n">
+        <f aca="false">ROUND(K15*$P$3,2)</f>
+        <v>1.26</v>
       </c>
       <c r="F15" s="5" t="n">
         <f aca="false">D15*E15</f>
-        <v>905.3</v>
+        <v>1036.98</v>
       </c>
       <c r="H15" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="I15" s="26" t="n">
+      <c r="I15" s="28" t="n">
         <f aca="false">D15/H15</f>
         <v>2.35142857142857</v>
       </c>
       <c r="J15" s="4"/>
+      <c r="K15" s="15" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>109</v>
@@ -4823,28 +4916,32 @@
       <c r="D16" s="15" t="n">
         <v>2097</v>
       </c>
-      <c r="E16" s="15" t="n">
-        <v>1.1</v>
+      <c r="E16" s="5" t="n">
+        <f aca="false">ROUND(K16*$P$3,2)</f>
+        <v>1.26</v>
       </c>
       <c r="F16" s="5" t="n">
         <f aca="false">D16*E16</f>
-        <v>2306.7</v>
+        <v>2642.22</v>
       </c>
       <c r="H16" s="24" t="n">
         <v>250</v>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I16" s="28" t="n">
         <f aca="false">D16/H16</f>
         <v>8.388</v>
       </c>
       <c r="J16" s="4"/>
+      <c r="K16" s="15" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>42</v>
@@ -4852,22 +4949,26 @@
       <c r="D17" s="15" t="n">
         <v>82.9</v>
       </c>
-      <c r="E17" s="15" t="n">
-        <v>25</v>
+      <c r="E17" s="5" t="n">
+        <f aca="false">ROUND(K17*$P$3,2)</f>
+        <v>28.7</v>
       </c>
       <c r="F17" s="5" t="n">
         <f aca="false">D17*E17</f>
-        <v>2072.5</v>
+        <v>2379.23</v>
       </c>
       <c r="H17" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="26" t="n">
+      <c r="I17" s="28" t="n">
         <f aca="false">D17/H17</f>
         <v>6.90833333333333</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4875,7 +4976,7 @@
         <v>86</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>42</v>
@@ -4884,28 +4985,32 @@
         <f aca="false">Metrados!$E$23</f>
         <v>7.4</v>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>5</v>
+      <c r="E18" s="5" t="n">
+        <f aca="false">ROUND(K18*$P$3,2)</f>
+        <v>5.74</v>
       </c>
       <c r="F18" s="5" t="n">
         <f aca="false">D18*E18</f>
-        <v>37</v>
+        <v>42.476</v>
       </c>
       <c r="H18" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I18" s="28" t="n">
         <f aca="false">D18/H18</f>
         <v>0.148</v>
       </c>
       <c r="J18" s="4"/>
+      <c r="K18" s="15" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>49</v>
@@ -4913,30 +5018,34 @@
       <c r="D19" s="15" t="n">
         <v>38.2</v>
       </c>
-      <c r="E19" s="15" t="n">
-        <v>40</v>
+      <c r="E19" s="5" t="n">
+        <f aca="false">ROUND(K19*$P$3,2)</f>
+        <v>45.93</v>
       </c>
       <c r="F19" s="5" t="n">
         <f aca="false">D19*E19</f>
-        <v>1528</v>
+        <v>1754.526</v>
       </c>
       <c r="H19" s="24" t="n">
         <v>38.2</v>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="28" t="n">
         <f aca="false">D19/H19</f>
         <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>109</v>
@@ -4944,22 +5053,26 @@
       <c r="D20" s="15" t="n">
         <v>2646</v>
       </c>
-      <c r="E20" s="15" t="n">
-        <v>1.3</v>
+      <c r="E20" s="5" t="n">
+        <f aca="false">ROUND(K20*$P$3,2)</f>
+        <v>1.49</v>
       </c>
       <c r="F20" s="5" t="n">
         <f aca="false">D20*E20</f>
-        <v>3439.8</v>
+        <v>3942.54</v>
       </c>
       <c r="H20" s="24" t="n">
         <v>200</v>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I20" s="28" t="n">
         <f aca="false">D20/H20</f>
         <v>13.23</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
+      </c>
+      <c r="K20" s="15" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4967,7 +5080,7 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>42</v>
@@ -4976,28 +5089,32 @@
         <f aca="false">Metrados!$E$27</f>
         <v>83.5</v>
       </c>
-      <c r="E21" s="15" t="n">
-        <v>28</v>
+      <c r="E21" s="5" t="n">
+        <f aca="false">ROUND(K21*$P$3,2)</f>
+        <v>32.15</v>
       </c>
       <c r="F21" s="5" t="n">
         <f aca="false">D21*E21</f>
-        <v>2338</v>
+        <v>2684.525</v>
       </c>
       <c r="H21" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="26" t="n">
+      <c r="I21" s="28" t="n">
         <f aca="false">D21/H21</f>
         <v>8.35</v>
       </c>
       <c r="J21" s="4"/>
+      <c r="K21" s="15" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>95</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>49</v>
@@ -5005,30 +5122,34 @@
       <c r="D22" s="15" t="n">
         <v>8.8</v>
       </c>
-      <c r="E22" s="15" t="n">
-        <v>60</v>
+      <c r="E22" s="5" t="n">
+        <f aca="false">ROUND(K22*$P$3,2)</f>
+        <v>68.89</v>
       </c>
       <c r="F22" s="5" t="n">
         <f aca="false">D22*E22</f>
-        <v>528</v>
+        <v>606.232</v>
       </c>
       <c r="H22" s="24" t="n">
         <v>8.8</v>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I22" s="28" t="n">
         <f aca="false">D22/H22</f>
         <v>1</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>109</v>
@@ -5036,28 +5157,32 @@
       <c r="D23" s="15" t="n">
         <v>304</v>
       </c>
-      <c r="E23" s="15" t="n">
-        <v>1.2</v>
+      <c r="E23" s="5" t="n">
+        <f aca="false">ROUND(K23*$P$3,2)</f>
+        <v>1.38</v>
       </c>
       <c r="F23" s="5" t="n">
         <f aca="false">D23*E23</f>
-        <v>364.8</v>
+        <v>419.52</v>
       </c>
       <c r="H23" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="I23" s="26" t="n">
+      <c r="I23" s="28" t="n">
         <f aca="false">D23/H23</f>
         <v>2.02666666666667</v>
       </c>
       <c r="J23" s="4"/>
+      <c r="K23" s="15" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>42</v>
@@ -5066,28 +5191,32 @@
         <f aca="false">Metrados!$E$29</f>
         <v>21.9</v>
       </c>
-      <c r="E24" s="15" t="n">
-        <v>25</v>
+      <c r="E24" s="5" t="n">
+        <f aca="false">ROUND(K24*$P$3,2)</f>
+        <v>28.7</v>
       </c>
       <c r="F24" s="5" t="n">
         <f aca="false">D24*E24</f>
-        <v>547.5</v>
+        <v>628.53</v>
       </c>
       <c r="H24" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="28" t="n">
         <f aca="false">D24/H24</f>
         <v>2.19</v>
       </c>
       <c r="J24" s="4"/>
+      <c r="K24" s="15" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>49</v>
@@ -5095,28 +5224,32 @@
       <c r="D25" s="15" t="n">
         <v>0.37</v>
       </c>
-      <c r="E25" s="15" t="n">
-        <v>120</v>
+      <c r="E25" s="5" t="n">
+        <f aca="false">ROUND(K25*$P$3,2)</f>
+        <v>137.78</v>
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">D25*E25</f>
-        <v>44.4</v>
+        <v>50.9786</v>
       </c>
       <c r="H25" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="28" t="n">
         <f aca="false">D25/H25</f>
         <v>0.185</v>
       </c>
       <c r="J25" s="4"/>
+      <c r="K25" s="15" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>113</v>
@@ -5125,28 +5258,32 @@
         <f aca="false">Metrados!$E$31</f>
         <v>8</v>
       </c>
-      <c r="E26" s="15" t="n">
-        <v>20</v>
+      <c r="E26" s="5" t="n">
+        <f aca="false">ROUND(K26*$P$3,2)</f>
+        <v>22.96</v>
       </c>
       <c r="F26" s="5" t="n">
         <f aca="false">D26*E26</f>
-        <v>160</v>
+        <v>183.68</v>
       </c>
       <c r="H26" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="28" t="n">
         <f aca="false">D26/H26</f>
         <v>0.5</v>
       </c>
       <c r="J26" s="4"/>
+      <c r="K26" s="15" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>115</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>42</v>
@@ -5155,28 +5292,32 @@
         <f aca="false">Metrados!$E$33</f>
         <v>29.8</v>
       </c>
-      <c r="E27" s="15" t="n">
-        <v>35</v>
+      <c r="E27" s="5" t="n">
+        <f aca="false">ROUND(K27*$P$3,2)</f>
+        <v>40.19</v>
       </c>
       <c r="F27" s="5" t="n">
         <f aca="false">D27*E27</f>
-        <v>1043</v>
+        <v>1197.662</v>
       </c>
       <c r="H27" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="28" t="n">
         <f aca="false">D27/H27</f>
         <v>2.98</v>
       </c>
       <c r="J27" s="4"/>
+      <c r="K27" s="15" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
         <v>117</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>42</v>
@@ -5185,21 +5326,25 @@
         <f aca="false">Metrados!$E$34</f>
         <v>66.6</v>
       </c>
-      <c r="E28" s="15" t="n">
-        <v>35</v>
+      <c r="E28" s="5" t="n">
+        <f aca="false">ROUND(K28*$P$3,2)</f>
+        <v>40.19</v>
       </c>
       <c r="F28" s="5" t="n">
         <f aca="false">D28*E28</f>
-        <v>2331</v>
+        <v>2676.654</v>
       </c>
       <c r="H28" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I28" s="28" t="n">
         <f aca="false">D28/H28</f>
         <v>6.66</v>
       </c>
       <c r="J28" s="4"/>
+      <c r="K28" s="15" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
@@ -5215,59 +5360,67 @@
         <f aca="false">Metrados!$E$35</f>
         <v>48</v>
       </c>
-      <c r="E29" s="15" t="n">
-        <v>8</v>
+      <c r="E29" s="5" t="n">
+        <f aca="false">ROUND(K29*$P$3,2)</f>
+        <v>9.19</v>
       </c>
       <c r="F29" s="5" t="n">
         <f aca="false">D29*E29</f>
-        <v>384</v>
+        <v>441.12</v>
       </c>
       <c r="H29" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="I29" s="26" t="n">
+      <c r="I29" s="28" t="n">
         <f aca="false">D29/H29</f>
         <v>0.8</v>
       </c>
       <c r="J29" s="4"/>
+      <c r="K29" s="15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
         <v>125</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="E30" s="15" t="n">
-        <v>40</v>
+      <c r="E30" s="5" t="n">
+        <f aca="false">ROUND(K30*$P$3,2)</f>
+        <v>45.93</v>
       </c>
       <c r="F30" s="5" t="n">
         <f aca="false">D30*E30</f>
-        <v>560</v>
+        <v>643.02</v>
       </c>
       <c r="H30" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="I30" s="26" t="n">
+      <c r="I30" s="28" t="n">
         <f aca="false">D30/H30</f>
         <v>1</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>127</v>
@@ -5275,25 +5428,29 @@
       <c r="D31" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="15" t="n">
-        <v>300</v>
+      <c r="E31" s="5" t="n">
+        <f aca="false">ROUND(K31*$P$3,2)</f>
+        <v>344.45</v>
       </c>
       <c r="F31" s="5" t="n">
         <f aca="false">D31*E31</f>
-        <v>300</v>
+        <v>344.45</v>
       </c>
       <c r="H31" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="26" t="n">
+      <c r="I31" s="28" t="n">
         <f aca="false">D31/H31</f>
         <v>1</v>
       </c>
       <c r="J31" s="4"/>
+      <c r="K31" s="15" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>127</v>
@@ -5301,11 +5458,15 @@
       <c r="D32" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="15" t="n">
-        <v>2500</v>
+      <c r="E32" s="5" t="n">
+        <f aca="false">ROUND(K32*$P$3,2)</f>
+        <v>2870.38</v>
       </c>
       <c r="F32" s="5" t="n">
         <f aca="false">D32*E32</f>
+        <v>2870.38</v>
+      </c>
+      <c r="K32" s="15" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -5315,23 +5476,23 @@
       </c>
       <c r="F33" s="8" t="n">
         <f aca="false">SUM(F5:F32)</f>
-        <v>30738.3</v>
+        <v>35985.2648</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="I33" s="27" t="n">
+        <v>346</v>
+      </c>
+      <c r="I33" s="29" t="n">
         <f aca="false">SUM(I5:I31)</f>
-        <v>80.0950714285714</v>
+        <v>81.9572142857143</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E34" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="F34" s="29" t="n">
-        <f aca="false">CEILING(F33,500)</f>
-        <v>31000</v>
+      <c r="E34" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <f aca="false">ROUND(F33,-2)</f>
+        <v>36000</v>
       </c>
     </row>
   </sheetData>
@@ -5360,12 +5521,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5373,68 +5534,68 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="B5" s="26" t="n">
+        <v>352</v>
+      </c>
+      <c r="B5" s="28" t="n">
         <f aca="false">'Mano de obra'!$I$33</f>
-        <v>80.0950714285714</v>
+        <v>81.9572142857143</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B6" s="30" t="n">
+        <v>354</v>
+      </c>
+      <c r="B6" s="32" t="n">
         <v>1.35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B7" s="31" t="n">
+        <v>356</v>
+      </c>
+      <c r="B7" s="33" t="n">
         <v>0.1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B8" s="32" t="n">
+        <v>358</v>
+      </c>
+      <c r="B8" s="34" t="n">
         <f aca="false">ROUNDUP(B5/B6*(1+B7),0)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B9" s="26" t="n">
+        <v>360</v>
+      </c>
+      <c r="B9" s="28" t="n">
         <f aca="false">B8/6</f>
-        <v>11</v>
+        <v>11.1666666666667</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5442,108 +5603,108 @@
       <c r="C10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>358</v>
+      <c r="A11" s="30" t="s">
+        <v>362</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="B12" s="32" t="n">
+        <v>363</v>
+      </c>
+      <c r="B12" s="34" t="n">
         <f aca="false">B8*Precios!$D$32</f>
-        <v>8580</v>
+        <v>8710</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="B13" s="32" t="n">
+        <v>364</v>
+      </c>
+      <c r="B13" s="34" t="n">
         <f aca="false">B8*Precios!$D$33</f>
-        <v>5280</v>
+        <v>5360</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="B14" s="32" t="n">
+        <v>365</v>
+      </c>
+      <c r="B14" s="34" t="n">
         <f aca="false">6*Precios!$D$33</f>
         <v>480</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B15" s="32" t="n">
+        <v>367</v>
+      </c>
+      <c r="B15" s="34" t="n">
         <f aca="false">13*Precios!$D$30</f>
         <v>1950</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="32" t="n">
+        <v>210</v>
+      </c>
+      <c r="B16" s="34" t="n">
         <f aca="false">Precios!$D$31</f>
         <v>300</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="B17" s="32" t="n">
+        <v>370</v>
+      </c>
+      <c r="B17" s="34" t="n">
         <f aca="false">Precios!$D$36</f>
         <v>1000</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B18" s="32" t="n">
+        <v>372</v>
+      </c>
+      <c r="B18" s="34" t="n">
         <f aca="false">Precios!$D$37</f>
         <v>400</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="B19" s="32" t="n">
+        <v>373</v>
+      </c>
+      <c r="B19" s="34" t="n">
         <f aca="false">Precios!$D$39*Precios!$D$38</f>
         <v>3040</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="B20" s="32" t="n">
+        <v>375</v>
+      </c>
+      <c r="B20" s="34" t="n">
         <f aca="false">Precios!$D$40</f>
         <v>900</v>
       </c>
@@ -5551,42 +5712,42 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B21" s="33" t="n">
+        <v>376</v>
+      </c>
+      <c r="B21" s="35" t="n">
         <v>600</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B22" s="33" t="n">
+        <v>378</v>
+      </c>
+      <c r="B22" s="35" t="n">
         <v>400</v>
       </c>
       <c r="C22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B23" s="33" t="n">
+        <v>379</v>
+      </c>
+      <c r="B23" s="35" t="n">
         <v>600</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B24" s="34" t="n">
+        <v>381</v>
+      </c>
+      <c r="B24" s="36" t="n">
         <f aca="false">SUM(B12:B23)</f>
-        <v>23530</v>
+        <v>23740</v>
       </c>
       <c r="C24" s="4"/>
     </row>
@@ -5596,95 +5757,95 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B26" s="34" t="n">
+        <v>382</v>
+      </c>
+      <c r="B26" s="36" t="n">
         <f aca="false">'Mano de obra'!$F$34</f>
-        <v>31000</v>
+        <v>36000</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B27" s="34" t="n">
+        <v>384</v>
+      </c>
+      <c r="B27" s="36" t="n">
         <f aca="false">B26-B24</f>
-        <v>7470</v>
+        <v>12260</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="B28" s="32" t="n">
+        <v>386</v>
+      </c>
+      <c r="B28" s="34" t="n">
         <f aca="false">(B17+B18+B19+B20)*Precios!$D$41</f>
         <v>2403</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B29" s="34" t="n">
+        <v>388</v>
+      </c>
+      <c r="B29" s="36" t="n">
         <f aca="false">B27+B28</f>
-        <v>9873</v>
+        <v>14663</v>
       </c>
       <c r="C29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="B30" s="32" t="n">
+        <v>389</v>
+      </c>
+      <c r="B30" s="34" t="n">
         <f aca="false">B29/B9</f>
-        <v>897.545454545455</v>
+        <v>1313.10447761194</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B31" s="6" t="n">
         <f aca="false">B29/B26</f>
-        <v>0.318483870967742</v>
+        <v>0.407305555555556</v>
       </c>
       <c r="C31" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="B35" s="32" t="n">
+      <c r="B35" s="34" t="n">
         <f aca="false">B29-(50-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>13233</v>
+        <v>18233</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -5692,9 +5853,9 @@
       <c r="A36" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="34" t="n">
         <f aca="false">B29-(60-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>11133</v>
+        <v>16133</v>
       </c>
       <c r="C36" s="4"/>
     </row>
@@ -5702,9 +5863,9 @@
       <c r="A37" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="B37" s="32" t="n">
+      <c r="B37" s="34" t="n">
         <f aca="false">B29-(70-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>9033</v>
+        <v>14033</v>
       </c>
       <c r="C37" s="4"/>
     </row>
@@ -5712,9 +5873,9 @@
       <c r="A38" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="B38" s="32" t="n">
+      <c r="B38" s="34" t="n">
         <f aca="false">B29-(80-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>6933</v>
+        <v>11933</v>
       </c>
       <c r="C38" s="4"/>
     </row>
@@ -5722,9 +5883,9 @@
       <c r="A39" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="B39" s="32" t="n">
+      <c r="B39" s="34" t="n">
         <f aca="false">B29-(90-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>4833</v>
+        <v>9833</v>
       </c>
       <c r="C39" s="4"/>
     </row>

--- a/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
+++ b/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="406">
   <si>
     <t xml:space="preserve">COTIZACIÓN ETAPA 1 - VIVIENDA UNIFAMILIAR, CHORRILLOS</t>
   </si>
@@ -115,13 +115,13 @@
     <t xml:space="preserve">Materiales a precio de tienda con IGV; el premezclado y la bomba deben confirmarse con 2-3 concreteras. Validez: 15 días.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nivel de VE según E-10 (de -1.00 a -0.30 sobre tecnopor). Si se cambia, se ajusta concreto, encofrado y excavación.</t>
+    <t xml:space="preserve">VE de -1.50 a -0.80 conectadas a las zapatas. Sistema mixto: linderos A y C de albañilería confinada (muro endentado de KK portante antes del vaciado de columnas).</t>
   </si>
   <si>
     <t xml:space="preserve">ETAPA 1 - METRADOS VERIFICADOS (E-10 vs. revisión)</t>
   </si>
   <si>
-    <t xml:space="preserve">Revisión del cuadro E-10 contra E-01, E-02/E-03, E-04. Filas en naranja = corregidas. VE de -1.00 a -0.30 sobre tecnopor (zanja de 1.10 de E-10).</t>
+    <t xml:space="preserve">Revisión del cuadro E-10 contra E-01, E-02/E-03, E-04. Filas en naranja = corregidas. VE de -1.50 a -0.80 conectadas a las zapatas (tecnopor debajo entre zapatas). Sistema mixto: albañilería confinada en linderos A y C.</t>
   </si>
   <si>
     <t xml:space="preserve">Ítem</t>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">Excavación zanjas VE / VC (retroexcavadora)</t>
   </si>
   <si>
-    <t xml:space="preserve">VE 0.70×1.10×24.53 m = 18.9; VC 0.55×1.50×6.56 m = 5.4</t>
+    <t xml:space="preserve">VE ahora con fondo -1.50 + tecnopor: 0.70×1.60×24.53 = 27.5; VC 0.55×1.50×6.56 = 5.4. (El modelo, descontando el sobreancho de pozos, da 28.3)</t>
   </si>
   <si>
     <t xml:space="preserve">02.03</t>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">Relleno compactado con material propio hasta -0.20</t>
   </si>
   <si>
-    <t xml:space="preserve">Vivienda: 111.4 excav. - 44.9 enterrado (incl. sobrecimiento bajo -0.20) - 14.5 (capa superior 0.20) = 52.0; cerco 7.3. E-10 79.4 NO CABE en la excavación</t>
+    <t xml:space="preserve">Vivienda: excavación bajo -0.20 = 104.9 - enterrado 41.7 (solado, zapatas, VE, VC, tecnopor, columnas, sobrecimiento) = 63.2; cerco 7.3</t>
   </si>
   <si>
     <t xml:space="preserve">02.05</t>
@@ -214,7 +214,7 @@
     <t xml:space="preserve">Eliminación de material excedente (esponj. 25%)</t>
   </si>
   <si>
-    <t xml:space="preserve">(124.7 - 59.3) × 1.25. E-10 sale bajo porque su relleno está inflado</t>
+    <t xml:space="preserve">(133.3 - 70.5) × 1.25</t>
   </si>
   <si>
     <t xml:space="preserve">03  CONCRETO SIMPLE</t>
@@ -244,7 +244,7 @@
     <t xml:space="preserve">Sobrecimiento 1:8 + 25% PM 0.15 de ancho (perímetro + cerco)</t>
   </si>
   <si>
-    <t xml:space="preserve">Debe arrancar desde la viga, no desde -0.20: sobre VE (top -0.30) h = 0.50 → 20.98 m; sobre VC de ejes A y C (top -1.10) h ≈ 1.25 → 10.72 m; cerco h = 0.40 → 11.78 m</t>
+    <t xml:space="preserve">Arranca desde la viga: sobre VE (top -0.80) h = 1.00 → 20.98 m; sobre VC de ejes A y C (top -1.10 / zapata -1.00) h 1.20-1.30 → 10.72 m; cerco h = 0.40 → 11.78 m (medido en el modelo)</t>
   </si>
   <si>
     <t xml:space="preserve">03.04</t>
@@ -253,7 +253,7 @@
     <t xml:space="preserve">Encofrado de sobrecimiento (2 caras)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 × (0.50 × 20.98 + 1.25 × 10.72 + 0.40 × 11.78)</t>
+    <t xml:space="preserve">2 × (1.00 × 20.98 + 1.25 × 10.72 + 0.40 × 11.78)</t>
   </si>
   <si>
     <t xml:space="preserve">04  CONCRETO ARMADO f'c 210</t>
@@ -271,10 +271,10 @@
     <t xml:space="preserve">04.02</t>
   </si>
   <si>
-    <t xml:space="preserve">Vigas de equilibrio VE 0.30×0.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-10 solo mide 24.5 m entre zapatas. Con VE de -1.00 a -0.30 la viga va ENCIMA de la zapata: también se vacía el tramo sobre zapata (30.95 m). 0.21 × 55.47</t>
+    <t xml:space="preserve">Vigas de equilibrio VE 0.30×0.70 (de -1.50 a -0.80)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entre zapatas 0.30×0.70×24.53 = 5.15 + sobre zapata solo lo que sobresale (-1.00 a -0.80) 0.30×0.20×30.95 = 1.86</t>
   </si>
   <si>
     <t xml:space="preserve">04.03</t>
@@ -283,13 +283,13 @@
     <t xml:space="preserve">Encofrado VE (2 caras)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 × 0.70 × 55.47 (también sobre la zapata)</t>
+    <t xml:space="preserve">2 × 0.70 × 24.53 + 2 × 0.20 × 30.95</t>
   </si>
   <si>
     <t xml:space="preserve">04.04</t>
   </si>
   <si>
-    <t xml:space="preserve">Tecnopor e = 0.10 bajo VE (solo entre zapatas)</t>
+    <t xml:space="preserve">Tecnopor e = 0.10 bajo VE (solo entre zapatas, de -1.60 a -1.50)</t>
   </si>
   <si>
     <t xml:space="preserve">0.30 × 24.53</t>
@@ -319,7 +319,7 @@
     <t xml:space="preserve">Columnas 1er piso (-1.00 a +2.30)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49 m² × 3.30</t>
+    <t xml:space="preserve">2.49 m² × 3.30 = 8.22 + 0.10 de concreto que entra en los dientes del muro</t>
   </si>
   <si>
     <t xml:space="preserve">04.07</t>
@@ -328,7 +328,7 @@
     <t xml:space="preserve">Encofrado columnas 1er piso</t>
   </si>
   <si>
-    <t xml:space="preserve">Perímetros 25.3 m × 3.30</t>
+    <t xml:space="preserve">25.3 m × 3.30 = 83.5 - 16 caras contra muro endentado (0.13 × 2.10) = 4.4</t>
   </si>
   <si>
     <t xml:space="preserve">04.08</t>
@@ -379,678 +379,711 @@
     <t xml:space="preserve">Muro cerco delantero</t>
   </si>
   <si>
-    <t xml:space="preserve">05.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muro perímetro vivienda hasta +2.30 (altura final del 1er nivel, con junta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7 m × 2.10 (de +0.20 a +2.30, fondo de viga). E-10 paraba en +2.00</t>
+    <t xml:space="preserve">05.02a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muro portante linderos A y C - KK PORTANTE endentado (albañilería confinada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 × 12.50 × 2.10 (de +0.20 a +2.30). Se levanta ANTES de vaciar las columnas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05.02b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muro fondo eje 5 - tabique KK 18 huecos con junta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70 × 2.10</t>
   </si>
   <si>
     <t xml:space="preserve">05.03</t>
   </si>
   <si>
+    <t xml:space="preserve">Junta con tecnopor 1" (solo fondo y encuentro cerco-vivienda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linderos ya no llevan junta (muro endentado). Fondo 4 × 2.10 + cerco-vivienda 2 × 2.60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06  VARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curado de concreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensayo de probetas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMBIOS DE OBRA: VE de -1.50 a -0.80 conectadas a las zapatas (tecnopor 0.10 bajo VE entre zapatas, excavación a -1.60).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistema mixto: linderos A y C de albañilería confinada (KK portante con ≤30% vacíos, E.070), muro endentado y luego vaciado de columnas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero de columnas 1er piso: 2,646 kg (E-10) verificado (barras Ø5/8" de 6.00 m de arranque + estribos Ø1/2" 1,342 kg + montaje 3/8" 38 kg).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diferencias menores a favor (no se cambian): zanjas de VE medidas sin descontar el sobreancho de los pozos (~2.5 m³ de más); encofrado de columnas sin descontar las caras donde llega la VE (~6.7 m²).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRECIOS DE MATERIALES Y SERVICIOS - Lima, octubre 2026 (con IGV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZUL = editable. Fuente principal: tu Excel (Sodimac / mercado oct-2026). Cambia aquí y todo se recalcula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insumo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concreto premezclado f'c 210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercado Lima S/ 260-320 (tu Excel 300). Se usa 320 por seguridad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bomba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba de concreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S/ 35-40/m³, mínimo 20 m³ por vaciado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cemento GU / Tipo I 42.5 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bolsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena gruesa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu Excel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra chancada 1/2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hormigón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra grande 6"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra mediana 4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varilla Ø3/4" × 9 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">varilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varilla Ø5/8" × 9 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varilla Ø1/2" × 9 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varilla Ø3/8" × 9 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varilla 6 mm × 9 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">al16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alambre N°16 rollo 100 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">al8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alambre N°8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clavo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clavos 2"-4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladrillo KK 18 huecos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kkp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladrillo KK PORTANTE (≤30% vacíos, tipo IV/V) 9×13×24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu Excel: S/ 1.50-2.20 (cotizar, pedir ficha técnica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnopor 4" plancha 1.20×2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plancha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnopor 1" plancha 1.20×2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">epox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epóxico para anclajes (cartucho)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impermeabilizante asfáltico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volquete 18 m³ eliminación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">viaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu Excel (C&amp;M Chamana)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apisonador / plancha compactadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">día</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensayo de probetas (juego de 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasolina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retroexcavadora con operador (mín. 5 h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu dato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trasl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traslado de retroexcavadora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supuesto (confirmar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">op</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operario (jornal informal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu Excel (ObraMaestra S/ 120-160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ayudante / peón (jornal informal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu Excel (S/ 70-90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mezc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alquiler mezcladora (trompo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vibr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alquiler vibrador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trompo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trompo (mezcladora) - compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vibc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vibradora de concreto - compra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triplay fenólico film 18 mm 1.22×2.44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac: S/ 85-107 por 10 o más unidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad de planchas fenólicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83 m² de VE+VC a la vez, 3 piezas de 0.70×1.22 por plancha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listones, estacas, tensores y tirafondos para encofrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supuesto: ~60 listones 2"x3"x10' + accesorios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor que te queda en equipos y encofrado al terminar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trompo/vibradora ~75%, fenólico tras 4-5 usos ~30%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATERIALES - ETAPA 1 (cantidades por despiece real de varillas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concreto estructural con premezclado + bomba. Mezclas menores (solado, ciclópeo, sobrecimiento, solera, mortero) en obra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N°</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.U. (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcial (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cómo se calculó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. CONCRETO PREMEZCLADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premezclado f'c 210 - vaciado 1: zapatas + VE + VC + ZC + VA cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(23.39 + 7.01 + 0.66 + 1.36 + 1.18) × 1.04 = 34.9 + 2.0 por sobreexcavación de la retro → 37.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba - vaciado 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premezclado f'c 210 - vaciado 2: columnas 1er piso + CA cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8.22 + 0.60) × 1.04 = 9.2 → pedir 9.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba - vaciado 2 (cobra mínimo 20 m³)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columnas de 3.30 m: el mixer solo no llega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. MEZCLAS EN OBRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cemento (solado, ciclópeo, sobrecimiento, solera, mortero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solado 17 + ciclópeo 7 + sobrecim. 23 + solera 4 + mortero 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hormigón (solado, ciclópeo, sobrecimiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4 + 1.9 + 5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena gruesa (solera + mortero de muros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 + 96.6 m² × 0.028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra chancada 1/2" (solera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra grande 6" (ciclópeo 30%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra mediana 4" (sobrecimiento 25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. ACERO (por despiece de barras de 9 m, no por kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VE en ejes 1-5 continua (8.8 m = 1 varilla por barra): 32; VE en ejes A, B, C: 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columnas 136 (arranque 6.00, sobra 3.00 → se usa en zapatas) + zapatas 29 + VE 22 + VC 18 + cerco 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estribos columnas 1,342 kg + cerco 177 kg, +5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estribos VE 381 und (4 por varilla) 96 + VC 86 und 13 + montaje 9 + cerco 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerco 27 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alambre N°16 (3% del acero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. ENCOFRADO Y OTROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alambre N°8 (encofrado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25 kg/m² × 231 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clavos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15 kg/m² × 231 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladrillo KK PORTANTE - linderos A y C (+5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5 m² × 39 × 1.05. Obligatorio en muro portante zona 4 (E.070)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladrillo KK 18 huecos - fondo y cerco (+5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(14.1 + 30.0) m² × 39 × 1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnopor 4" bajo VE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4 m² ÷ 2.88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnopor 1" para juntas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6 ml × 0.13 ≈ 1.8 m² + cortes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epóxico para anclajes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 anclajes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impermeabilizante asfáltico (sobrecimiento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EQUIPOS Y SERVICIOS QUE PAGA EL CLIENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eliminación de desmonte - volquete 18 m³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5 m³ suelto ÷ 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alquiler de apisonador para relleno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5 m³ ÷ 8 m³/día</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 por vaciado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combustible apisonador, trompo y vibrador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua para obra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flete de fierro y agregados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negociar flete gratis en pedido grande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANO DE OBRA "POR UN TANTO" - PRECIO AL CLIENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio por partida (destajo Lima). La excavación incluye la retroexcavadora y el carguío. Columnas H-J: uso interno (rendimiento de tu cuadrilla operario + ayudante).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio objetivo MO (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.U. MO (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rend. cuadrilla (und/día)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días-cuadrilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.U. base (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavación con retroexcavadora (zapatas + zanjas) y carguío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máquina: ver hoja Mi costo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfilado y nivelación de fondos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pozos 54.4 + zanjas VE 17.2 + VC 3.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavación manual cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relleno compactado con material propio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con apisonador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cimiento corrido ciclópeo cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sobrecimiento - vaciado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado y desencofrado de sobrecimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.09a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero zapatas - habilitado y colocado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.09b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero VE y VC - habilitado y colocado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado y desencofrado VE y VC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VE 46.7 + VC 5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colocación de tecnopor bajo VE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaciado y vibrado premezclado - cimentación (37 m³)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 día + eventuales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.09c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero columnas - habilitado y colocado (estribos densos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-10 nota 5: fierrería alta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado y desencofrado columnas (h = 3.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaciado y vibrado premezclado - columnas + CA (contra muro endentado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con bomba, 1 día</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.09d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado y desencofrado cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04.08c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concreto solera cerco (hecho en obra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anclajes con epóxico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muro KK de soga - cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muro portante KK endentado - linderos (albañilería confinada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Más lento: endentado y plomo para confinar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muro KK de soga - fondo (tabique con junta)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junta con tecnopor 1"</t>
   </si>
   <si>
-    <t xml:space="preserve">ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-10 42.0 + 20 juntas muro-columna × 0.30 adicionales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06  VARIOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curado de concreto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ensayo de probetas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPORTANTE - NIVEL DE LA VE: E-10 usa VE de -1.00 a -0.30 (zanja de 1.10 y tecnopor debajo). Si la VE va con fondo a -1.50 (al mismo nivel que la zapata),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">el concreto de VE baja a 7.0 m³ y el encofrado a 46.7 m², pero la zanja de VE sube a 1.60 de profundidad (27.5 m³). Definir antes de comprar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acero de columnas 1er piso: 2,646 kg (E-10) verificado (barras Ø5/8" de 6.00 m de arranque + estribos Ø1/2" 1,342 kg + montaje 3/8" 38 kg).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diferencias menores a favor (no se cambian): zanjas de VE medidas sin descontar el sobreancho de los pozos (~2.5 m³ de más); encofrado de columnas sin descontar las caras donde llega la VE (~6.7 m²).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRECIOS DE MATERIALES Y SERVICIOS - Lima, octubre 2026 (con IGV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZUL = editable. Fuente principal: tu Excel (Sodimac / mercado oct-2026). Cambia aquí y todo se recalcula.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Código</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insumo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio (S/)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concreto premezclado f'c 210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercado Lima S/ 260-320 (tu Excel 300). Se usa 320 por seguridad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bomba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomba de concreto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S/ 35-40/m³, mínimo 20 m³ por vaciado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cemento GU / Tipo I 42.5 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bolsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sodimac oct-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">are</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arena gruesa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tu Excel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piedra chancada 1/2"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hormigón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piedra grande 6"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piedra mediana 4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varilla Ø3/4" × 9 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">varilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varilla Ø5/8" × 9 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varilla Ø1/2" × 9 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varilla Ø3/8" × 9 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varilla 6 mm × 9 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">al16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alambre N°16 rollo 100 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">al8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alambre N°8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referencial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clavo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clavos 2"-4"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ladrillo KK 18 huecos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sodimac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tecnopor 4" plancha 1.20×2.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plancha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tecnopor 1" plancha 1.20×2.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epóxico para anclajes (cartucho)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impermeabilizante asfáltico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">volq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Volquete 18 m³ eliminación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tu Excel (C&amp;M Chamana)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apisonador / plancha compactadora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">día</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ensayo de probetas (juego de 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">retro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retroexcavadora con operador (mín. 5 h)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tu dato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trasl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traslado de retroexcavadora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supuesto (confirmar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">op</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operario (jornal informal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tu Excel (ObraMaestra S/ 120-160)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ayudante / peón (jornal informal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tu Excel (S/ 70-90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mezc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alquiler mezcladora (trompo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vibr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alquiler vibrador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trompo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trompo (mezcladora) - compra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vibc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vibradora de concreto - compra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triplay fenólico film 18 mm 1.22×2.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sodimac: S/ 85-107 por 10 o más unidades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nfen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cantidad de planchas fenólicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83 m² de VE+VC a la vez, 3 piezas de 0.70×1.22 por plancha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Listones, estacas, tensores y tirafondos para encofrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supuesto: ~60 listones 2"x3"x10' + accesorios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor que te queda en equipos y encofrado al terminar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trompo/vibradora ~75%, fenólico tras 4-5 usos ~30%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MATERIALES - ETAPA 1 (cantidades por despiece real de varillas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concreto estructural con premezclado + bomba. Mezclas menores (solado, ciclópeo, sobrecimiento, solera, mortero) en obra.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N°</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cantidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.U. (S/)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcial (S/)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cómo se calculó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A. CONCRETO PREMEZCLADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premezclado f'c 210 - vaciado 1: zapatas + VE + VC + ZC + VA cerco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(23.39 + 11.65 + 0.66 + 1.36 + 1.18) × 1.04 = 39.8 + 2.0 por sobreexcavación de la retro → 42.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomba - vaciado 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premezclado f'c 210 - vaciado 2: columnas 1er piso + CA cerco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.22 + 0.60) × 1.04 = 9.2 → pedir 9.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomba - vaciado 2 (cobra mínimo 20 m³)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columnas de 3.30 m: el mixer solo no llega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B. MEZCLAS EN OBRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cemento (solado, ciclópeo, sobrecimiento, solera, mortero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solado 17 + ciclópeo 7 + sobrecim. 17 + solera 4 + mortero 22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hormigón (solado, ciclópeo, sobrecimiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4 + 1.9 + 3.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arena gruesa (solera + mortero de muros)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2 + 96.6 m² × 0.028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piedra chancada 1/2" (solera)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piedra grande 6" (ciclópeo 30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piedra mediana 4" (sobrecimiento 25%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C. ACERO (por despiece de barras de 9 m, no por kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VE en ejes 1-5 continua (8.8 m = 1 varilla por barra): 32; VE en ejes A, B, C: 40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columnas 136 (arranque 6.00, sobra 3.00 → se usa en zapatas) + zapatas 29 + VE 22 + VC 18 + cerco 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estribos columnas 1,342 kg + cerco 177 kg, +5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estribos VE 381 und (4 por varilla) 96 + VC 86 und 13 + montaje 9 + cerco 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerco 27 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alambre N°16 (3% del acero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D. ENCOFRADO Y OTROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alambre N°8 (encofrado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25 kg/m² × 246 m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clavos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15 kg/m² × 246 m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ladrillo KK 18 huecos (+5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.6 m² × 39 × 1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tecnopor 4" bajo VE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4 m² ÷ 2.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tecnopor 1" para juntas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≈ 13.5 m² ÷ 2.88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epóxico para anclajes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 anclajes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Impermeabilizante asfáltico (sobrecimiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPOS Y SERVICIOS QUE PAGA EL CLIENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eliminación de desmonte - volquete 18 m³</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7 m³ suelto ÷ 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alquiler de apisonador para relleno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59 m³ ÷ 8 m³/día</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 por vaciado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combustible apisonador, trompo y vibrador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agua para obra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flete de fierro y agregados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negociar flete gratis en pedido grande</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANO DE OBRA "POR UN TANTO" - PRECIO AL CLIENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio por partida (destajo Lima). La excavación incluye la retroexcavadora y el carguío. Columnas H-J: uso interno (rendimiento de tu cuadrilla operario + ayudante).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precio objetivo MO (S/)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.U. MO (S/)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rend. cuadrilla (und/día)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Días-cuadrilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.U. base (S/)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excavación con retroexcavadora (zapatas + zanjas) y carguío</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Máquina: ver hoja Mi costo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfilado y nivelación de fondos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pozos 54.4 + zanjas VE 17.2 + VC 3.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excavación manual cerco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relleno compactado con material propio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con apisonador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cimiento corrido ciclópeo cerco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sobrecimiento - vaciado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encofrado y desencofrado de sobrecimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.09a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acero zapatas - habilitado y colocado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.09b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acero VE y VC - habilitado y colocado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encofrado y desencofrado VE y VC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VE 77.7 + VC 5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colocación de tecnopor bajo VE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaciado y vibrado premezclado - cimentación (42 m³)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 día + eventuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.09c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acero columnas - habilitado y colocado (estribos densos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-10 nota 5: fierrería alta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encofrado y desencofrado columnas (h = 3.30)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaciado y vibrado premezclado - columnas + CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con bomba, 1 día</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.09d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acero cerco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Encofrado y desencofrado cerco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04.08c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concreto solera cerco (hecho en obra)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anclajes con epóxico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muro KK de soga - cerco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muro KK de soga - perímetro vivienda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curado de concreto (riego diario)</t>
   </si>
   <si>
@@ -1129,10 +1162,10 @@
     <t xml:space="preserve">1 día cada uno</t>
   </si>
   <si>
-    <t xml:space="preserve">Retroexcavadora: 13 h (mín. 5 h por día)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excavación 111 m³ + carguío de 5 volquetes</t>
+    <t xml:space="preserve">Retroexcavadora: 14 h (mín. 5 h por día)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavación 120 m³ + carguío de 5 volquetes</t>
   </si>
   <si>
     <t xml:space="preserve">Confirmar si está incluido</t>
@@ -1846,12 +1879,12 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">Materiales!$F$32</f>
-        <v>54431.49</v>
+        <f aca="false">Materiales!$F$33</f>
+        <v>53866.39</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">B5/$B$10</f>
-        <v>0.554835612431767</v>
+        <v>0.551644314127364</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
@@ -1863,11 +1896,11 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">'Equipos y servicios'!$F$11</f>
-        <v>4715</v>
+        <v>4845</v>
       </c>
       <c r="C6" s="6" t="n">
         <f aca="false">B6/$B$10</f>
-        <v>0.048061332008655</v>
+        <v>0.0496175203489055</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>9</v>
@@ -1878,12 +1911,12 @@
         <v>10</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">'Mano de obra'!$F$34</f>
+        <f aca="false">'Mano de obra'!$F$35</f>
         <v>36000</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">B7/$B$10</f>
-        <v>0.366958208337557</v>
+        <v>0.368675073799917</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
@@ -1895,11 +1928,11 @@
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">SUM(B5:B7)</f>
-        <v>95146.49</v>
+        <v>94711.39</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">B8/$B$10</f>
-        <v>0.969855152777979</v>
+        <v>0.969936908276187</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1908,11 +1941,11 @@
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">0.05*(B5+B6)</f>
-        <v>2957.3245</v>
+        <v>2935.5695</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">B9/$B$10</f>
-        <v>0.0301448472220211</v>
+        <v>0.0300630917238135</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>14</v>
@@ -1924,7 +1957,7 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">B8+B9</f>
-        <v>98103.8145</v>
+        <v>97646.9595</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">B10/$B$10</f>
@@ -2065,7 +2098,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -2203,27 +2236,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="19" t="n">
         <v>24.3</v>
       </c>
-      <c r="E10" s="15" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="20" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="F10" s="21" t="n">
         <f aca="false">E10-D10</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="17" t="s">
+        <v>8.6</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2265,11 +2298,11 @@
         <v>79.4</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>59.3</v>
+        <v>70.5</v>
       </c>
       <c r="F12" s="21" t="n">
         <f aca="false">E12-D12</f>
-        <v>-20.1</v>
+        <v>-8.90000000000001</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>59</v>
@@ -2289,11 +2322,11 @@
         <v>53.5</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>81.7</v>
+        <v>78.5</v>
       </c>
       <c r="F13" s="21" t="n">
         <f aca="false">E13-D13</f>
-        <v>28.2</v>
+        <v>25</v>
       </c>
       <c r="G13" s="22" t="s">
         <v>62</v>
@@ -2372,11 +2405,11 @@
         <v>2.7</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>4.29</v>
+        <v>5.85</v>
       </c>
       <c r="F17" s="21" t="n">
         <f aca="false">E17-D17</f>
-        <v>1.59</v>
+        <v>3.15</v>
       </c>
       <c r="G17" s="22" t="s">
         <v>72</v>
@@ -2396,11 +2429,11 @@
         <v>35.4</v>
       </c>
       <c r="E18" s="20" t="n">
-        <v>57.2</v>
+        <v>78</v>
       </c>
       <c r="F18" s="21" t="n">
         <f aca="false">E18-D18</f>
-        <v>21.8</v>
+        <v>42.6</v>
       </c>
       <c r="G18" s="22" t="s">
         <v>75</v>
@@ -2455,11 +2488,11 @@
         <v>5.2</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>11.65</v>
+        <v>7.01</v>
       </c>
       <c r="F21" s="21" t="n">
         <f aca="false">E21-D21</f>
-        <v>6.45</v>
+        <v>1.81</v>
       </c>
       <c r="G21" s="22" t="s">
         <v>82</v>
@@ -2479,11 +2512,11 @@
         <v>34.4</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>77.7</v>
+        <v>46.7</v>
       </c>
       <c r="F22" s="21" t="n">
         <f aca="false">E22-D22</f>
-        <v>43.3</v>
+        <v>12.3</v>
       </c>
       <c r="G22" s="22" t="s">
         <v>85</v>
@@ -2575,37 +2608,37 @@
         <v>8.2</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>8.22</v>
+        <v>8.32</v>
       </c>
       <c r="F26" s="16" t="n">
         <f aca="false">E26-D26</f>
-        <v>0.0200000000000014</v>
+        <v>0.120000000000001</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="19" t="n">
         <v>83.5</v>
       </c>
-      <c r="E27" s="15" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="20" t="n">
+        <v>79.1</v>
+      </c>
+      <c r="F27" s="21" t="n">
         <f aca="false">E27-D27</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="17" t="s">
+        <v>-4.40000000000001</v>
+      </c>
+      <c r="G27" s="22" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2752,11 +2785,11 @@
         <v>57.1</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>66.6</v>
+        <v>52.5</v>
       </c>
       <c r="F34" s="21" t="n">
         <f aca="false">E34-D34</f>
-        <v>9.49999999999999</v>
+        <v>-4.6</v>
       </c>
       <c r="G34" s="22" t="s">
         <v>119</v>
@@ -2770,54 +2803,56 @@
         <v>121</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>48</v>
+        <v>14.1</v>
       </c>
       <c r="F35" s="21" t="n">
         <f aca="false">E35-D35</f>
-        <v>6</v>
+        <v>14.1</v>
       </c>
       <c r="G35" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="13" t="s">
+      <c r="B36" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="C36" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F36" s="21" t="n">
+        <f aca="false">E36-D36</f>
+        <v>-28.4</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" s="4" t="s">
+      <c r="A37" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <f aca="false">E37-D37</f>
-        <v>0</v>
-      </c>
-      <c r="G37" s="17"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
@@ -2830,10 +2865,10 @@
         <v>130</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F38" s="16" t="n">
         <f aca="false">E38-D38</f>
@@ -2841,24 +2876,46 @@
       </c>
       <c r="G38" s="17"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
         <v>131</v>
       </c>
+      <c r="B39" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <f aca="false">E39-D39</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="23" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2877,7 +2934,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -2889,37 +2946,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>49</v>
@@ -2928,15 +2985,15 @@
         <v>320</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>49</v>
@@ -2945,32 +3002,32 @@
         <v>38</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>28.6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>49</v>
@@ -2979,15 +3036,15 @@
         <v>65</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -2996,15 +3053,15 @@
         <v>80</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>49</v>
@@ -3013,15 +3070,15 @@
         <v>60</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>49</v>
@@ -3030,15 +3087,15 @@
         <v>50</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -3047,117 +3104,117 @@
         <v>50</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>80.02</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>54.41</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>35.96</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D16" s="15" t="n">
         <v>20.06</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D17" s="15" t="n">
         <v>7.96</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D18" s="15" t="n">
         <v>349.9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>109</v>
@@ -3166,15 +3223,15 @@
         <v>6.5</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>109</v>
@@ -3183,15 +3240,15 @@
         <v>7.5</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>113</v>
@@ -3200,347 +3257,364 @@
         <v>1.14</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>55</v>
+        <v>1.6</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="D24" s="15" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D26" s="15" t="n">
-        <v>460</v>
+        <v>45</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="D28" s="15" t="n">
-        <v>75</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>127</v>
+        <v>213</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>113</v>
+        <v>206</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>113</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="D38" s="15" t="n">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="D40" s="15" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D42" s="15" t="n">
         <v>0.45</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>237</v>
+      <c r="E42" s="4" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3559,7 +3633,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3572,40 +3646,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -3619,13 +3693,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">Precios!$D$5</f>
@@ -3633,10 +3707,10 @@
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
-        <v>13440</v>
+        <v>11840</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3644,13 +3718,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">Precios!$D$6</f>
@@ -3658,7 +3732,7 @@
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">D7*E7</f>
-        <v>1596</v>
+        <v>1406</v>
       </c>
       <c r="G7" s="4"/>
     </row>
@@ -3667,7 +3741,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>49</v>
@@ -3684,7 +3758,7 @@
         <v>3040</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3692,7 +3766,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -3709,12 +3783,12 @@
         <v>760</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -3728,13 +3802,13 @@
         <v>5</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">Precios!$D$7</f>
@@ -3742,10 +3816,10 @@
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">D11*E11</f>
-        <v>1916.2</v>
+        <v>2087.8</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3753,13 +3827,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">Precios!$D$10</f>
@@ -3767,10 +3841,10 @@
       </c>
       <c r="F12" s="5" t="n">
         <f aca="false">D12*E12</f>
-        <v>660</v>
+        <v>744</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3778,7 +3852,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
@@ -3795,7 +3869,7 @@
         <v>195</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3803,7 +3877,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>49</v>
@@ -3826,7 +3900,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>49</v>
@@ -3849,13 +3923,13 @@
         <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="E16" s="5" t="n">
         <f aca="false">Precios!$D$12</f>
@@ -3863,13 +3937,13 @@
       </c>
       <c r="F16" s="5" t="n">
         <f aca="false">D16*E16</f>
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -3883,10 +3957,10 @@
         <v>11</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>72</v>
@@ -3900,7 +3974,7 @@
         <v>5761.44</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3908,10 +3982,10 @@
         <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>207</v>
@@ -3925,7 +3999,7 @@
         <v>11262.87</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3933,10 +4007,10 @@
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>179</v>
@@ -3950,7 +4024,7 @@
         <v>6436.84</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3958,10 +4032,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>134</v>
@@ -3975,7 +4049,7 @@
         <v>2688.04</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3983,10 +4057,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>15</v>
@@ -4000,7 +4074,7 @@
         <v>119.4</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4008,10 +4082,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>2</v>
@@ -4025,12 +4099,12 @@
         <v>699.8</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -4044,13 +4118,13 @@
         <v>17</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">Precios!$D$19</f>
@@ -4058,10 +4132,10 @@
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">D25*E25</f>
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4069,13 +4143,13 @@
         <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>109</v>
       </c>
       <c r="D26" s="24" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">Precios!$D$20</f>
@@ -4083,10 +4157,10 @@
       </c>
       <c r="F26" s="5" t="n">
         <f aca="false">D26*E26</f>
-        <v>277.5</v>
+        <v>262.5</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4094,24 +4168,24 @@
         <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>113</v>
       </c>
       <c r="D27" s="24" t="n">
-        <v>3960</v>
+        <v>2150</v>
       </c>
       <c r="E27" s="5" t="n">
-        <f aca="false">Precios!$D$21</f>
-        <v>1.14</v>
+        <f aca="false">Precios!$D$22</f>
+        <v>1.6</v>
       </c>
       <c r="F27" s="5" t="n">
         <f aca="false">D27*E27</f>
-        <v>4514.4</v>
+        <v>3440</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4119,24 +4193,24 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="D28" s="24" t="n">
-        <v>3</v>
+        <v>1805</v>
       </c>
       <c r="E28" s="5" t="n">
-        <f aca="false">Precios!$D$22</f>
-        <v>55</v>
+        <f aca="false">Precios!$D$21</f>
+        <v>1.14</v>
       </c>
       <c r="F28" s="5" t="n">
         <f aca="false">D28*E28</f>
-        <v>165</v>
+        <v>2057.7</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4144,24 +4218,24 @@
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D29" s="24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">Precios!$D$23</f>
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F29" s="5" t="n">
         <f aca="false">D29*E29</f>
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4169,24 +4243,24 @@
         <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="D30" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">Precios!$D$24</f>
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="F30" s="5" t="n">
         <f aca="false">D30*E30</f>
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4194,31 +4268,56 @@
         <v>23</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="D31" s="24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">Precios!$D$25</f>
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="F31" s="5" t="n">
         <f aca="false">D31*E31</f>
-        <v>135</v>
-      </c>
-      <c r="G31" s="4"/>
+        <v>120</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E32" s="7" t="s">
+      <c r="A32" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <f aca="false">Precios!$D$26</f>
+        <v>45</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <f aca="false">D32*E32</f>
+        <v>180</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <f aca="false">SUM(F5:F31)</f>
-        <v>54431.49</v>
+      <c r="F33" s="8" t="n">
+        <f aca="false">SUM(F5:F32)</f>
+        <v>53866.39</v>
       </c>
     </row>
   </sheetData>
@@ -4251,7 +4350,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4259,7 +4358,7 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -4268,16 +4367,16 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4285,16 +4384,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">Precios!$D$26</f>
+        <f aca="false">Precios!$D$27</f>
         <v>460</v>
       </c>
       <c r="F5" s="5" t="n">
@@ -4302,7 +4401,7 @@
         <v>2300</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4310,24 +4409,24 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="n">
-        <f aca="false">Precios!$D$27</f>
+        <f aca="false">Precios!$D$28</f>
         <v>130</v>
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
-        <v>1040</v>
+        <v>1170</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4335,16 +4434,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>5</v>
       </c>
       <c r="E7" s="5" t="n">
-        <f aca="false">Precios!$D$28</f>
+        <f aca="false">Precios!$D$29</f>
         <v>75</v>
       </c>
       <c r="F7" s="5" t="n">
@@ -4352,7 +4451,7 @@
         <v>375</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4360,16 +4459,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>20</v>
       </c>
       <c r="E8" s="5" t="n">
-        <f aca="false">Precios!$D$29</f>
+        <f aca="false">Precios!$D$30</f>
         <v>20</v>
       </c>
       <c r="F8" s="5" t="n">
@@ -4383,10 +4482,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D9" s="25" t="n">
         <v>1</v>
@@ -4405,10 +4504,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D10" s="25" t="n">
         <v>1</v>
@@ -4421,7 +4520,7 @@
         <v>300</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,7 +4529,7 @@
       </c>
       <c r="F11" s="8" t="n">
         <f aca="false">SUM(F5:F10)</f>
-        <v>4715</v>
+        <v>4845</v>
       </c>
     </row>
   </sheetData>
@@ -4449,7 +4548,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -4470,27 +4569,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M3" s="9" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="N3" s="26" t="n">
         <v>36000</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="P3" s="27" t="n">
-        <f aca="false">N3/SUMPRODUCT(D5:D32,K5:K32)</f>
-        <v>1.14815322742683</v>
+        <f aca="false">N3/SUMPRODUCT(D5:D33,K5:K33)</f>
+        <v>1.14206676014695</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4504,26 +4603,26 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4542,11 +4641,11 @@
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">ROUND(K5*$P$3,2)</f>
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">D5*E5</f>
-        <v>391</v>
+        <v>387.6</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>170</v>
@@ -4576,11 +4675,11 @@
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">ROUND(K6*$P$3,2)</f>
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="F6" s="5" t="n">
         <f aca="false">D6*E6</f>
-        <v>584.8</v>
+        <v>583.1</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>170</v>
@@ -4599,31 +4698,31 @@
         <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">Metrados!$E$9+Metrados!$E$10</f>
-        <v>111.4</v>
+        <v>120</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">ROUND(K7*$P$3,2)</f>
-        <v>36.74</v>
+        <v>36.55</v>
       </c>
       <c r="F7" s="5" t="n">
         <f aca="false">D7*E7</f>
-        <v>4092.836</v>
+        <v>4386</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="I7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="K7" s="15" t="n">
         <v>32</v>
@@ -4634,7 +4733,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>42</v>
@@ -4644,11 +4743,11 @@
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">ROUND(K8*$P$3,2)</f>
-        <v>6.89</v>
+        <v>6.85</v>
       </c>
       <c r="F8" s="5" t="n">
         <f aca="false">D8*E8</f>
-        <v>518.128</v>
+        <v>515.12</v>
       </c>
       <c r="H8" s="24" t="n">
         <v>25</v>
@@ -4658,7 +4757,7 @@
         <v>3.008</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>6</v>
@@ -4669,7 +4768,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -4680,11 +4779,11 @@
       </c>
       <c r="E9" s="5" t="n">
         <f aca="false">ROUND(K9*$P$3,2)</f>
-        <v>51.67</v>
+        <v>51.39</v>
       </c>
       <c r="F9" s="5" t="n">
         <f aca="false">D9*E9</f>
-        <v>687.211</v>
+        <v>683.487</v>
       </c>
       <c r="H9" s="24" t="n">
         <v>4</v>
@@ -4703,32 +4802,32 @@
         <v>57</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">Metrados!$E$12</f>
-        <v>59.3</v>
+        <v>70.5</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">ROUND(K10*$P$3,2)</f>
-        <v>34.44</v>
+        <v>34.26</v>
       </c>
       <c r="F10" s="5" t="n">
         <f aca="false">D10*E10</f>
-        <v>2042.292</v>
+        <v>2415.33</v>
       </c>
       <c r="H10" s="24" t="n">
         <v>8</v>
       </c>
       <c r="I10" s="28" t="n">
         <f aca="false">D10/H10</f>
-        <v>7.4125</v>
+        <v>8.8125</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>30</v>
@@ -4739,7 +4838,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>42</v>
@@ -4750,11 +4849,11 @@
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">ROUND(K11*$P$3,2)</f>
-        <v>17.22</v>
+        <v>17.13</v>
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">D11*E11</f>
-        <v>861</v>
+        <v>856.5</v>
       </c>
       <c r="H11" s="24" t="n">
         <v>35</v>
@@ -4773,7 +4872,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -4784,11 +4883,11 @@
       </c>
       <c r="E12" s="5" t="n">
         <f aca="false">ROUND(K12*$P$3,2)</f>
-        <v>103.33</v>
+        <v>102.79</v>
       </c>
       <c r="F12" s="5" t="n">
         <f aca="false">D12*E12</f>
-        <v>227.326</v>
+        <v>226.138</v>
       </c>
       <c r="H12" s="24" t="n">
         <v>4</v>
@@ -4807,29 +4906,29 @@
         <v>70</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="5" t="n">
         <f aca="false">Metrados!$E$17</f>
-        <v>4.29</v>
+        <v>5.85</v>
       </c>
       <c r="E13" s="5" t="n">
         <f aca="false">ROUND(K13*$P$3,2)</f>
-        <v>137.78</v>
+        <v>137.05</v>
       </c>
       <c r="F13" s="5" t="n">
         <f aca="false">D13*E13</f>
-        <v>591.0762</v>
+        <v>801.7425</v>
       </c>
       <c r="H13" s="24" t="n">
         <v>3</v>
       </c>
       <c r="I13" s="28" t="n">
         <f aca="false">D13/H13</f>
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="15" t="n">
@@ -4841,29 +4940,29 @@
         <v>73</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D14" s="5" t="n">
         <f aca="false">Metrados!$E$18</f>
-        <v>57.2</v>
+        <v>78</v>
       </c>
       <c r="E14" s="5" t="n">
         <f aca="false">ROUND(K14*$P$3,2)</f>
-        <v>25.26</v>
+        <v>25.13</v>
       </c>
       <c r="F14" s="5" t="n">
         <f aca="false">D14*E14</f>
-        <v>1444.872</v>
+        <v>1960.14</v>
       </c>
       <c r="H14" s="24" t="n">
         <v>14</v>
       </c>
       <c r="I14" s="28" t="n">
         <f aca="false">D14/H14</f>
-        <v>4.08571428571429</v>
+        <v>5.57142857142857</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="15" t="n">
@@ -4872,10 +4971,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>109</v>
@@ -4905,10 +5004,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>109</v>
@@ -4941,31 +5040,31 @@
         <v>83</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>82.9</v>
+        <v>51.9</v>
       </c>
       <c r="E17" s="5" t="n">
         <f aca="false">ROUND(K17*$P$3,2)</f>
-        <v>28.7</v>
+        <v>28.55</v>
       </c>
       <c r="F17" s="5" t="n">
         <f aca="false">D17*E17</f>
-        <v>2379.23</v>
+        <v>1481.745</v>
       </c>
       <c r="H17" s="24" t="n">
         <v>12</v>
       </c>
       <c r="I17" s="28" t="n">
         <f aca="false">D17/H17</f>
-        <v>6.90833333333333</v>
+        <v>4.325</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>25</v>
@@ -4976,7 +5075,7 @@
         <v>86</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>42</v>
@@ -4987,11 +5086,11 @@
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">ROUND(K18*$P$3,2)</f>
-        <v>5.74</v>
+        <v>5.71</v>
       </c>
       <c r="F18" s="5" t="n">
         <f aca="false">D18*E18</f>
-        <v>42.476</v>
+        <v>42.254</v>
       </c>
       <c r="H18" s="24" t="n">
         <v>50</v>
@@ -5010,31 +5109,31 @@
         <v>77</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>38.2</v>
+        <v>33.6</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">ROUND(K19*$P$3,2)</f>
-        <v>45.93</v>
+        <v>45.68</v>
       </c>
       <c r="F19" s="5" t="n">
         <f aca="false">D19*E19</f>
-        <v>1754.526</v>
+        <v>1534.848</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>38.2</v>
+        <v>33.6</v>
       </c>
       <c r="I19" s="28" t="n">
         <f aca="false">D19/H19</f>
         <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="K19" s="15" t="n">
         <v>40</v>
@@ -5042,10 +5141,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>109</v>
@@ -5055,11 +5154,11 @@
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">ROUND(K20*$P$3,2)</f>
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="F20" s="5" t="n">
         <f aca="false">D20*E20</f>
-        <v>3942.54</v>
+        <v>3916.08</v>
       </c>
       <c r="H20" s="24" t="n">
         <v>200</v>
@@ -5069,7 +5168,7 @@
         <v>13.23</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K20" s="15" t="n">
         <v>1.3</v>
@@ -5080,29 +5179,29 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="5" t="n">
         <f aca="false">Metrados!$E$27</f>
-        <v>83.5</v>
+        <v>79.1</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">ROUND(K21*$P$3,2)</f>
-        <v>32.15</v>
+        <v>31.98</v>
       </c>
       <c r="F21" s="5" t="n">
         <f aca="false">D21*E21</f>
-        <v>2684.525</v>
+        <v>2529.618</v>
       </c>
       <c r="H21" s="24" t="n">
         <v>10</v>
       </c>
       <c r="I21" s="28" t="n">
         <f aca="false">D21/H21</f>
-        <v>8.35</v>
+        <v>7.91</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="15" t="n">
@@ -5114,31 +5213,31 @@
         <v>95</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>8.8</v>
+        <v>8.9</v>
       </c>
       <c r="E22" s="5" t="n">
         <f aca="false">ROUND(K22*$P$3,2)</f>
-        <v>68.89</v>
+        <v>68.52</v>
       </c>
       <c r="F22" s="5" t="n">
         <f aca="false">D22*E22</f>
-        <v>606.232</v>
+        <v>609.828</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>8.8</v>
+        <v>8.9</v>
       </c>
       <c r="I22" s="28" t="n">
         <f aca="false">D22/H22</f>
         <v>1</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="K22" s="15" t="n">
         <v>60</v>
@@ -5146,10 +5245,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>109</v>
@@ -5159,11 +5258,11 @@
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">ROUND(K23*$P$3,2)</f>
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="F23" s="5" t="n">
         <f aca="false">D23*E23</f>
-        <v>419.52</v>
+        <v>416.48</v>
       </c>
       <c r="H23" s="24" t="n">
         <v>150</v>
@@ -5182,7 +5281,7 @@
         <v>104</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>42</v>
@@ -5193,11 +5292,11 @@
       </c>
       <c r="E24" s="5" t="n">
         <f aca="false">ROUND(K24*$P$3,2)</f>
-        <v>28.7</v>
+        <v>28.55</v>
       </c>
       <c r="F24" s="5" t="n">
         <f aca="false">D24*E24</f>
-        <v>628.53</v>
+        <v>625.245</v>
       </c>
       <c r="H24" s="24" t="n">
         <v>10</v>
@@ -5213,10 +5312,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>49</v>
@@ -5226,11 +5325,11 @@
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">ROUND(K25*$P$3,2)</f>
-        <v>137.78</v>
+        <v>137.05</v>
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">D25*E25</f>
-        <v>50.9786</v>
+        <v>50.7085</v>
       </c>
       <c r="H25" s="24" t="n">
         <v>2</v>
@@ -5249,7 +5348,7 @@
         <v>111</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>113</v>
@@ -5260,11 +5359,11 @@
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">ROUND(K26*$P$3,2)</f>
-        <v>22.96</v>
+        <v>22.84</v>
       </c>
       <c r="F26" s="5" t="n">
         <f aca="false">D26*E26</f>
-        <v>183.68</v>
+        <v>182.72</v>
       </c>
       <c r="H26" s="24" t="n">
         <v>16</v>
@@ -5283,7 +5382,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>42</v>
@@ -5294,11 +5393,11 @@
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">ROUND(K27*$P$3,2)</f>
-        <v>40.19</v>
+        <v>39.97</v>
       </c>
       <c r="F27" s="5" t="n">
         <f aca="false">D27*E27</f>
-        <v>1197.662</v>
+        <v>1191.106</v>
       </c>
       <c r="H27" s="24" t="n">
         <v>10</v>
@@ -5317,33 +5416,35 @@
         <v>117</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="5" t="n">
         <f aca="false">Metrados!$E$34</f>
-        <v>66.6</v>
+        <v>52.5</v>
       </c>
       <c r="E28" s="5" t="n">
         <f aca="false">ROUND(K28*$P$3,2)</f>
-        <v>40.19</v>
+        <v>45.68</v>
       </c>
       <c r="F28" s="5" t="n">
         <f aca="false">D28*E28</f>
-        <v>2676.654</v>
+        <v>2398.2</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I28" s="28" t="n">
         <f aca="false">D28/H28</f>
-        <v>6.66</v>
-      </c>
-      <c r="J28" s="4"/>
+        <v>6.5625</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>349</v>
+      </c>
       <c r="K28" s="15" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5351,147 +5452,181 @@
         <v>120</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>121</v>
+        <v>350</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="D29" s="5" t="n">
         <f aca="false">Metrados!$E$35</f>
-        <v>48</v>
+        <v>14.1</v>
       </c>
       <c r="E29" s="5" t="n">
         <f aca="false">ROUND(K29*$P$3,2)</f>
-        <v>9.19</v>
+        <v>39.97</v>
       </c>
       <c r="F29" s="5" t="n">
         <f aca="false">D29*E29</f>
-        <v>441.12</v>
+        <v>563.577</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I29" s="28" t="n">
         <f aca="false">D29/H29</f>
-        <v>0.8</v>
+        <v>1.41</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="15" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>14</v>
+      <c r="D30" s="5" t="n">
+        <f aca="false">Metrados!$E$36</f>
+        <v>13.6</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">ROUND(K30*$P$3,2)</f>
-        <v>45.93</v>
+        <v>9.14</v>
       </c>
       <c r="F30" s="5" t="n">
         <f aca="false">D30*E30</f>
-        <v>643.02</v>
+        <v>124.304</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I30" s="28" t="n">
         <f aca="false">D30/H30</f>
-        <v>1</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>342</v>
-      </c>
+        <v>0.226666666666667</v>
+      </c>
+      <c r="J30" s="4"/>
       <c r="K30" s="15" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>343</v>
+        <v>128</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E31" s="5" t="n">
         <f aca="false">ROUND(K31*$P$3,2)</f>
-        <v>344.45</v>
+        <v>45.68</v>
       </c>
       <c r="F31" s="5" t="n">
         <f aca="false">D31*E31</f>
-        <v>344.45</v>
+        <v>639.52</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I31" s="28" t="n">
         <f aca="false">D31/H31</f>
         <v>1</v>
       </c>
-      <c r="J31" s="4"/>
+      <c r="J31" s="4" t="s">
+        <v>353</v>
+      </c>
       <c r="K31" s="15" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>354</v>
+      </c>
       <c r="B32" s="4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="25" t="n">
+        <v>130</v>
+      </c>
+      <c r="D32" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="5" t="n">
         <f aca="false">ROUND(K32*$P$3,2)</f>
-        <v>2870.38</v>
+        <v>342.62</v>
       </c>
       <c r="F32" s="5" t="n">
         <f aca="false">D32*E32</f>
-        <v>2870.38</v>
-      </c>
+        <v>342.62</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="28" t="n">
+        <f aca="false">D32/H32</f>
+        <v>1</v>
+      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="15" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <f aca="false">ROUND(K33*$P$3,2)</f>
+        <v>2855.17</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <f aca="false">D33*E33</f>
+        <v>2855.17</v>
+      </c>
+      <c r="K33" s="15" t="n">
         <v>2500</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="7" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <f aca="false">SUM(F5:F32)</f>
-        <v>35985.2648</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="I33" s="29" t="n">
-        <f aca="false">SUM(I5:I31)</f>
-        <v>81.9572142857143</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E34" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="F34" s="31" t="n">
-        <f aca="false">ROUND(F33,-2)</f>
+      <c r="F34" s="8" t="n">
+        <f aca="false">SUM(F5:F33)</f>
+        <v>35998.381</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <f aca="false">SUM(I5:I32)</f>
+        <v>83.0787619047619</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="F35" s="31" t="n">
+        <f aca="false">ROUND(F34,-2)</f>
         <v>36000</v>
       </c>
     </row>
@@ -5521,12 +5656,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5534,68 +5669,68 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B5" s="28" t="n">
-        <f aca="false">'Mano de obra'!$I$33</f>
-        <v>81.9572142857143</v>
+        <f aca="false">'Mano de obra'!$I$34</f>
+        <v>83.0787619047619</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B6" s="32" t="n">
         <v>1.35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B7" s="33" t="n">
         <v>0.1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B8" s="34" t="n">
         <f aca="false">ROUNDUP(B5/B6*(1+B7),0)</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B8/6</f>
-        <v>11.1666666666667</v>
+        <v>11.3333333333333</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5604,126 +5739,126 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B12" s="34" t="n">
-        <f aca="false">B8*Precios!$D$32</f>
-        <v>8710</v>
+        <f aca="false">B8*Precios!$D$33</f>
+        <v>8840</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B13" s="34" t="n">
-        <f aca="false">B8*Precios!$D$33</f>
-        <v>5360</v>
+        <f aca="false">B8*Precios!$D$34</f>
+        <v>5440</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B14" s="34" t="n">
-        <f aca="false">6*Precios!$D$33</f>
+        <f aca="false">6*Precios!$D$34</f>
         <v>480</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B15" s="34" t="n">
-        <f aca="false">13*Precios!$D$30</f>
-        <v>1950</v>
+        <f aca="false">14*Precios!$D$31</f>
+        <v>2100</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B16" s="34" t="n">
-        <f aca="false">Precios!$D$31</f>
+        <f aca="false">Precios!$D$32</f>
         <v>300</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B17" s="34" t="n">
-        <f aca="false">Precios!$D$36</f>
+        <f aca="false">Precios!$D$37</f>
         <v>1000</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B18" s="34" t="n">
-        <f aca="false">Precios!$D$37</f>
+        <f aca="false">Precios!$D$38</f>
         <v>400</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B19" s="34" t="n">
-        <f aca="false">Precios!$D$39*Precios!$D$38</f>
+        <f aca="false">Precios!$D$40*Precios!$D$39</f>
         <v>3040</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="B20" s="34" t="n">
-        <f aca="false">Precios!$D$40</f>
+        <f aca="false">Precios!$D$41</f>
         <v>900</v>
       </c>
       <c r="C20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B21" s="35" t="n">
         <v>600</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B22" s="35" t="n">
         <v>400</v>
@@ -5732,22 +5867,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B23" s="35" t="n">
         <v>600</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B24" s="36" t="n">
         <f aca="false">SUM(B12:B23)</f>
-        <v>23740</v>
+        <v>24100</v>
       </c>
       <c r="C24" s="4"/>
     </row>
@@ -5757,86 +5892,86 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B26" s="36" t="n">
-        <f aca="false">'Mano de obra'!$F$34</f>
+        <f aca="false">'Mano de obra'!$F$35</f>
         <v>36000</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B27" s="36" t="n">
         <f aca="false">B26-B24</f>
-        <v>12260</v>
+        <v>11900</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B28" s="34" t="n">
-        <f aca="false">(B17+B18+B19+B20)*Precios!$D$41</f>
+        <f aca="false">(B17+B18+B19+B20)*Precios!$D$42</f>
         <v>2403</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B29" s="36" t="n">
         <f aca="false">B27+B28</f>
-        <v>14663</v>
+        <v>14303</v>
       </c>
       <c r="C29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B30" s="34" t="n">
         <f aca="false">B29/B9</f>
-        <v>1313.10447761194</v>
+        <v>1262.02941176471</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B31" s="6" t="n">
         <f aca="false">B29/B26</f>
-        <v>0.407305555555556</v>
+        <v>0.397305555555556</v>
       </c>
       <c r="C31" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5844,8 +5979,8 @@
         <v>50</v>
       </c>
       <c r="B35" s="34" t="n">
-        <f aca="false">B29-(50-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>18233</v>
+        <f aca="false">B29-(50-B8)*(Precios!$D$33+Precios!$D$34)</f>
+        <v>18083</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -5854,8 +5989,8 @@
         <v>60</v>
       </c>
       <c r="B36" s="34" t="n">
-        <f aca="false">B29-(60-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>16133</v>
+        <f aca="false">B29-(60-B8)*(Precios!$D$33+Precios!$D$34)</f>
+        <v>15983</v>
       </c>
       <c r="C36" s="4"/>
     </row>
@@ -5864,8 +5999,8 @@
         <v>70</v>
       </c>
       <c r="B37" s="34" t="n">
-        <f aca="false">B29-(70-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>14033</v>
+        <f aca="false">B29-(70-B8)*(Precios!$D$33+Precios!$D$34)</f>
+        <v>13883</v>
       </c>
       <c r="C37" s="4"/>
     </row>
@@ -5874,8 +6009,8 @@
         <v>80</v>
       </c>
       <c r="B38" s="34" t="n">
-        <f aca="false">B29-(80-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>11933</v>
+        <f aca="false">B29-(80-B8)*(Precios!$D$33+Precios!$D$34)</f>
+        <v>11783</v>
       </c>
       <c r="C38" s="4"/>
     </row>
@@ -5884,8 +6019,8 @@
         <v>90</v>
       </c>
       <c r="B39" s="34" t="n">
-        <f aca="false">B29-(90-B8)*(Precios!$D$32+Precios!$D$33)</f>
-        <v>9833</v>
+        <f aca="false">B29-(90-B8)*(Precios!$D$33+Precios!$D$34)</f>
+        <v>9683</v>
       </c>
       <c r="C39" s="4"/>
     </row>

--- a/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
+++ b/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Equipos y servicios" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Mano de obra" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="INT Mi costo y ganancia" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="INT Opción A acero campo" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="465">
   <si>
     <t xml:space="preserve">COTIZACIÓN ETAPA 1 - VIVIENDA UNIFAMILIAR, CHORRILLOS</t>
   </si>
@@ -1244,6 +1245,183 @@
   </si>
   <si>
     <t xml:space="preserve">Mi ganancia real (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPCIÓN A - REDUCCIÓN DE ACERO EN VE Y VC (DECISIÓN DE CAMPO) - HOJA INTERNA, NO ENVIAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La cotización y los metrados se quedan con el acero del plano E-02/E-03. Esta hoja sirve para decidir en obra, ANTES de comprar y habilitar el fierro de vigas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mu (t·m) / T (t)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano: acero sup. / inf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">φMn plano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D/C plano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opción A: acero sup. / inf.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">φMn A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D/C A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VE-1 (4 und) h 0.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4Ø3/4"+1Ø5/8" / igual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3Ø3/4"+1Ø1/2" / 2Ø3/4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VE-2 (12 und) h 0.70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3Ø3/4"+1Ø5/8" / igual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VE momento positivo (inversión sísmica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verificar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">igual al superior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2Ø3/4" inferior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M+ ETABS ≤ 13.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VC (6 und) 0.25×0.40 - tracción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3Ø5/8" / 3Ø5/8"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2Ø5/8" / 2Ø5/8"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estribos sin cambio: □Ø3/8" 1@0.05, rto. @0.15 (VE) y @0.20 (VC). Mismos ganchos de 0.45 en columnas extremas. Sección y niveles sin cambio (VE de -1.50 a -0.80).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varillas de 9 m (VE + VC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano (cotizado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opción A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahorro (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ø3/4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 barras por tramo (antes 8 en eje 2 y 6 en el resto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ø5/8" en VE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La barra de 5/8" se reemplaza por 1/2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ø5/8" en VC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 barras por VC en vez de 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ø1/2" en VE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 barra superior por tramo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHORRO EN FIERRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unos 511 kg menos (VE 1,815 → 1,379 kg; VC 282 → 207 kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días de fierrería que te ahorras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimiento de 250 kg/día de la cuadrilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jornales que te ahorras (tu ganancia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La mano de obra cobrada sigue en S/ 36,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿QUIÉN SE QUEDA CON EL AHORRO?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• El fierro lo paga el cliente (compra directa): el ahorro en material es del cliente. Puedes ofrecerlo como mejora / descuento o compensarlo con un adicional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Lo tuyo es el tiempo: unos 2 días menos de fierrería con la misma mano de obra cobrada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONDICIONES PARA APLICARLA EN CAMPO (todas en SÍ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condición</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Cumple?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cómo se verifica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Momento positivo en VE (ETABS, 0.9D ± E) ≤ 13.1 t·m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar en el modelo, VE-1 y VE-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se decide ANTES de comprar el fierro de vigas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compra de fierro de VE va en la semana 2 (después de excavar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota firmada en cuaderno de obra o revisión del plano E-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como diseñador estructural, dejar constancia del cambio de armado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La barra de 1/2" va al centro, entre las 3 de 3/4" de arriba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las 3/4" van en las esquinas y al medio; 4 barras entran en una capa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empalmes y ganchos sin cambio (nota 6 y 9 del plano)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No empalmar sobre la zapata excéntrica ni en el primer tercio</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1618,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1586,6 +1764,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="173" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6033,4 +6231,427 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E5" s="37" t="n">
+        <f aca="false">B5/D5</f>
+        <v>0.660958904109589</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" s="37" t="n">
+        <f aca="false">B5/G5</f>
+        <v>0.877272727272727</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B6" s="28" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <f aca="false">B6/D6</f>
+        <v>0.794871794871795</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="H6" s="37" t="n">
+        <f aca="false">B6/G6</f>
+        <v>0.845454545454546</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>422</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H7" s="38" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B8" s="28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <f aca="false">B8/D8</f>
+        <v>0.11529933481153</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="H8" s="37" t="n">
+        <f aca="false">B8/G8</f>
+        <v>0.172757475083056</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="B12" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>55</v>
+      </c>
+      <c r="D12" s="25" t="n">
+        <f aca="false">C12-B12</f>
+        <v>-17</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <f aca="false">Precios!$D$13</f>
+        <v>80.02</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <f aca="false">-D12*E12</f>
+        <v>1360.34</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <f aca="false">C13-B13</f>
+        <v>-22</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <f aca="false">Precios!$D$14</f>
+        <v>54.41</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <f aca="false">-D13*E13</f>
+        <v>1197.02</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="25" t="n">
+        <f aca="false">C14-B14</f>
+        <v>-6</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <f aca="false">Precios!$D$14</f>
+        <v>54.41</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <f aca="false">-D14*E14</f>
+        <v>326.46</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" s="25" t="n">
+        <f aca="false">C15-B15</f>
+        <v>11</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <f aca="false">Precios!$D$15</f>
+        <v>35.96</v>
+      </c>
+      <c r="F15" s="34" t="n">
+        <f aca="false">-D15*E15</f>
+        <v>-395.56</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <f aca="false">SUM(F12:F15)</f>
+        <v>2488.26</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B17" s="28" t="n">
+        <f aca="false">511/250</f>
+        <v>2.044</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="F18" s="39" t="n">
+        <f aca="false">ROUND(B17/'INT Mi costo y ganancia'!B6*(Precios!$D$33+Precios!$D$34),0)</f>
+        <v>318</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="40" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="40" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B26" s="41"/>
+      <c r="C26" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B27" s="41"/>
+      <c r="C27" s="4" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B29" s="41"/>
+      <c r="C29" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
+++ b/metrados/Etapa1_Presupuesto_Informal_INTERNO.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="475">
   <si>
     <t xml:space="preserve">COTIZACIÓN ETAPA 1 - VIVIENDA UNIFAMILIAR, CHORRILLOS</t>
   </si>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">Sistema mixto: linderos A y C de albañilería confinada (KK portante con ≤30% vacíos, E.070), muro endentado y luego vaciado de columnas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Acero de columnas 1er piso: 2,646 kg (E-10) verificado (barras Ø5/8" de 6.00 m de arranque + estribos Ø1/2" 1,342 kg + montaje 3/8" 38 kg).</t>
+    <t xml:space="preserve">Acero de columnas 1er piso: barras Ø5/8" de 6.00 m de arranque + estribos TODOS en Ø3/8" (cambio de obra; E-04 pedía Ø1/2") + montaje 3/8".</t>
   </si>
   <si>
     <t xml:space="preserve">Diferencias menores a favor (no se cambian): zanjas de VE medidas sin descontar el sobreancho de los pozos (~2.5 m³ de más); encofrado de columnas sin descontar las caras donde llega la VE (~6.7 m²).</t>
@@ -752,6 +752,24 @@
     <t xml:space="preserve">Supuesto: ~60 listones 2"x3"x10' + accesorios</t>
   </si>
   <si>
+    <t xml:space="preserve">estcol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estribos Ø3/8" hechos columnas - proforma Benders 15/10/2026 (ítems 1-6, con IGV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,290 piezas: 430+430+86+86+129+129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estvig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estribos Ø3/8" hechos VE y VC - ESTIMADO (confirmar proforma corregida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">467 piezas, ~469 kg × S/ 5.3/kg (promedio de la proforma en Ø3/8")</t>
+  </si>
+  <si>
     <t xml:space="preserve">resid</t>
   </si>
   <si>
@@ -848,10 +866,22 @@
     <t xml:space="preserve">Columnas 136 (arranque 6.00, sobra 3.00 → se usa en zapatas) + zapatas 29 + VE 22 + VC 18 + cerco 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Estribos columnas 1,342 kg + cerco 177 kg, +5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estribos VE 381 und (4 por varilla) 96 + VC 86 und 13 + montaje 9 + cerco 16</t>
+    <t xml:space="preserve">Solo cerco (estribos 177 kg +5%): pendiente E-09. Los estribos de columnas y vigas van hechos, todos en Ø3/8"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje de columnas 9 + cerco 16 (los estribos de columnas y vigas van hechos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estribos Ø3/8" hechos - columnas (1,290 und, 43 por columna)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos en Ø3/8": 430 de 22×42 + 430 rectos 42 + 86 de 52×22 + 86 de 17.5×22 + 129 de 52×27 + 129 de 26×27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estribos Ø3/8" hechos - VE y VC (467 und)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">381 de 22×62 (VE) + 86 de 17×32 (VC). Precio estimado hasta recibir proforma corregida</t>
   </si>
   <si>
     <t xml:space="preserve">Cerco 27 kg</t>
@@ -2077,12 +2107,12 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">Materiales!$F$33</f>
-        <v>53866.39</v>
+        <f aca="false">Materiales!$F$35</f>
+        <v>52791.72</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">B5/$B$10</f>
-        <v>0.551644314127364</v>
+        <v>0.546959281073372</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
@@ -2098,7 +2128,7 @@
       </c>
       <c r="C6" s="6" t="n">
         <f aca="false">B6/$B$10</f>
-        <v>0.0496175203489055</v>
+        <v>0.050197601381438</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>9</v>
@@ -2114,7 +2144,7 @@
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">B7/$B$10</f>
-        <v>0.368675073799917</v>
+        <v>0.372985273422449</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
@@ -2126,11 +2156,11 @@
       </c>
       <c r="B8" s="8" t="n">
         <f aca="false">SUM(B5:B7)</f>
-        <v>94711.39</v>
+        <v>93636.72</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">B8/$B$10</f>
-        <v>0.969936908276187</v>
+        <v>0.97014215587726</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2139,11 +2169,11 @@
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">0.05*(B5+B6)</f>
-        <v>2935.5695</v>
+        <v>2881.836</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">B9/$B$10</f>
-        <v>0.0300630917238135</v>
+        <v>0.0298578441227405</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>14</v>
@@ -2155,7 +2185,7 @@
       </c>
       <c r="B10" s="8" t="n">
         <f aca="false">B8+B9</f>
-        <v>97646.9595</v>
+        <v>96518.556</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">B10/$B$10</f>
@@ -3132,7 +3162,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -3806,13 +3836,47 @@
         <v>242</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.45</v>
+        <v>4293.55</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>243</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3831,7 +3895,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3844,40 +3908,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -3891,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>49</v>
@@ -3908,7 +3972,7 @@
         <v>11840</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3916,7 +3980,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
@@ -3939,7 +4003,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>49</v>
@@ -3956,7 +4020,7 @@
         <v>3040</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3964,7 +4028,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -3981,12 +4045,12 @@
         <v>760</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -4000,7 +4064,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>152</v>
@@ -4017,7 +4081,7 @@
         <v>2087.8</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4025,7 +4089,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -4042,7 +4106,7 @@
         <v>744</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4050,7 +4114,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
@@ -4067,7 +4131,7 @@
         <v>195</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4075,7 +4139,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>49</v>
@@ -4098,7 +4162,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>49</v>
@@ -4121,7 +4185,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>49</v>
@@ -4141,7 +4205,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -4172,7 +4236,7 @@
         <v>5761.44</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4197,7 +4261,7 @@
         <v>11262.87</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4211,7 +4275,7 @@
         <v>167</v>
       </c>
       <c r="D20" s="24" t="n">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="E20" s="5" t="n">
         <f aca="false">Precios!$D$15</f>
@@ -4219,10 +4283,10 @@
       </c>
       <c r="F20" s="5" t="n">
         <f aca="false">D20*E20</f>
-        <v>6436.84</v>
+        <v>755.16</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4236,7 +4300,7 @@
         <v>167</v>
       </c>
       <c r="D21" s="24" t="n">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="E21" s="5" t="n">
         <f aca="false">Precios!$D$16</f>
@@ -4244,10 +4308,10 @@
       </c>
       <c r="F21" s="5" t="n">
         <f aca="false">D21*E21</f>
-        <v>2688.04</v>
+        <v>501.5</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4255,24 +4319,24 @@
         <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>175</v>
+        <v>281</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="D22" s="24" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E22" s="5" t="n">
-        <f aca="false">Precios!$D$17</f>
-        <v>7.96</v>
+        <f aca="false">Precios!$D$42</f>
+        <v>4293.55</v>
       </c>
       <c r="F22" s="5" t="n">
         <f aca="false">D22*E22</f>
-        <v>119.4</v>
+        <v>4293.55</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4280,110 +4344,110 @@
         <v>16</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <f aca="false">Precios!$D$43</f>
+        <v>2500</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <f aca="false">D23*E23</f>
+        <v>2500</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <f aca="false">Precios!$D$17</f>
+        <v>7.96</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <f aca="false">D24*E24</f>
+        <v>119.4</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D25" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E25" s="5" t="n">
         <f aca="false">Precios!$D$18</f>
         <v>349.9</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <f aca="false">D23*E23</f>
-        <v>699.8</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="24" t="n">
-        <v>58</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <f aca="false">Precios!$D$19</f>
-        <v>6.5</v>
-      </c>
       <c r="F25" s="5" t="n">
         <f aca="false">D25*E25</f>
-        <v>377</v>
+        <v>699.8</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="24" t="n">
-        <v>35</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <f aca="false">Precios!$D$20</f>
-        <v>7.5</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <f aca="false">D26*E26</f>
-        <v>262.5</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>282</v>
-      </c>
+      <c r="A26" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D27" s="24" t="n">
-        <v>2150</v>
+        <v>58</v>
       </c>
       <c r="E27" s="5" t="n">
-        <f aca="false">Precios!$D$22</f>
-        <v>1.6</v>
+        <f aca="false">Precios!$D$19</f>
+        <v>6.5</v>
       </c>
       <c r="F27" s="5" t="n">
         <f aca="false">D27*E27</f>
-        <v>3440</v>
+        <v>377</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4391,24 +4455,24 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D28" s="24" t="n">
-        <v>1805</v>
+        <v>35</v>
       </c>
       <c r="E28" s="5" t="n">
-        <f aca="false">Precios!$D$21</f>
-        <v>1.14</v>
+        <f aca="false">Precios!$D$20</f>
+        <v>7.5</v>
       </c>
       <c r="F28" s="5" t="n">
         <f aca="false">D28*E28</f>
-        <v>2057.7</v>
+        <v>262.5</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4416,24 +4480,24 @@
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>192</v>
+        <v>113</v>
       </c>
       <c r="D29" s="24" t="n">
-        <v>3</v>
+        <v>2150</v>
       </c>
       <c r="E29" s="5" t="n">
-        <f aca="false">Precios!$D$23</f>
-        <v>55</v>
+        <f aca="false">Precios!$D$22</f>
+        <v>1.6</v>
       </c>
       <c r="F29" s="5" t="n">
         <f aca="false">D29*E29</f>
-        <v>165</v>
+        <v>3440</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4441,24 +4505,24 @@
         <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>192</v>
+        <v>113</v>
       </c>
       <c r="D30" s="24" t="n">
-        <v>2</v>
+        <v>1805</v>
       </c>
       <c r="E30" s="5" t="n">
-        <f aca="false">Precios!$D$24</f>
-        <v>16</v>
+        <f aca="false">Precios!$D$21</f>
+        <v>1.14</v>
       </c>
       <c r="F30" s="5" t="n">
         <f aca="false">D30*E30</f>
-        <v>32</v>
+        <v>2057.7</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4466,24 +4530,24 @@
         <v>23</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="D31" s="24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5" t="n">
-        <f aca="false">Precios!$D$25</f>
-        <v>120</v>
+        <f aca="false">Precios!$D$23</f>
+        <v>55</v>
       </c>
       <c r="F31" s="5" t="n">
         <f aca="false">D31*E31</f>
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4491,31 +4555,81 @@
         <v>24</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <f aca="false">Precios!$D$24</f>
+        <v>16</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <f aca="false">D32*E32</f>
+        <v>32</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <f aca="false">Precios!$D$25</f>
+        <v>120</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <f aca="false">D33*E33</f>
+        <v>120</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="D32" s="24" t="n">
+      <c r="D34" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E34" s="5" t="n">
         <f aca="false">Precios!$D$26</f>
         <v>45</v>
       </c>
-      <c r="F32" s="5" t="n">
-        <f aca="false">D32*E32</f>
+      <c r="F34" s="5" t="n">
+        <f aca="false">D34*E34</f>
         <v>180</v>
       </c>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E33" s="7" t="s">
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <f aca="false">SUM(F5:F32)</f>
-        <v>53866.39</v>
+      <c r="F35" s="8" t="n">
+        <f aca="false">SUM(F5:F34)</f>
+        <v>52791.72</v>
       </c>
     </row>
   </sheetData>
@@ -4548,7 +4662,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4556,7 +4670,7 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -4565,16 +4679,16 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4582,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>202</v>
@@ -4599,7 +4713,7 @@
         <v>2300</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4607,7 +4721,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>206</v>
@@ -4624,7 +4738,7 @@
         <v>1170</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4649,7 +4763,7 @@
         <v>375</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4657,7 +4771,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>199</v>
@@ -4680,7 +4794,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>130</v>
@@ -4702,7 +4816,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>130</v>
@@ -4718,7 +4832,7 @@
         <v>300</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4767,23 +4881,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M3" s="9" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N3" s="26" t="n">
         <v>36000</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="P3" s="27" t="n">
         <f aca="false">N3/SUMPRODUCT(D5:D33,K5:K33)</f>
@@ -4801,26 +4915,26 @@
         <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4896,7 +5010,7 @@
         <v>47</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>49</v>
@@ -4914,13 +5028,13 @@
         <v>4386</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="I7" s="28" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="K7" s="15" t="n">
         <v>32</v>
@@ -4931,7 +5045,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>42</v>
@@ -4955,7 +5069,7 @@
         <v>3.008</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>6</v>
@@ -4966,7 +5080,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>49</v>
@@ -5000,7 +5114,7 @@
         <v>57</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>49</v>
@@ -5025,7 +5139,7 @@
         <v>8.8125</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>30</v>
@@ -5036,7 +5150,7 @@
         <v>64</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>42</v>
@@ -5070,7 +5184,7 @@
         <v>67</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>49</v>
@@ -5104,7 +5218,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>49</v>
@@ -5138,7 +5252,7 @@
         <v>73</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>42</v>
@@ -5169,10 +5283,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>109</v>
@@ -5202,10 +5316,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>109</v>
@@ -5238,7 +5352,7 @@
         <v>83</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>42</v>
@@ -5262,7 +5376,7 @@
         <v>4.325</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>25</v>
@@ -5273,7 +5387,7 @@
         <v>86</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>42</v>
@@ -5307,7 +5421,7 @@
         <v>77</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>49</v>
@@ -5331,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="K19" s="15" t="n">
         <v>40</v>
@@ -5339,10 +5453,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>109</v>
@@ -5366,7 +5480,7 @@
         <v>13.23</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="K20" s="15" t="n">
         <v>1.3</v>
@@ -5377,7 +5491,7 @@
         <v>98</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>42</v>
@@ -5411,7 +5525,7 @@
         <v>95</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>49</v>
@@ -5435,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="K22" s="15" t="n">
         <v>60</v>
@@ -5443,10 +5557,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>109</v>
@@ -5479,7 +5593,7 @@
         <v>104</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>42</v>
@@ -5510,10 +5624,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>49</v>
@@ -5546,7 +5660,7 @@
         <v>111</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>113</v>
@@ -5580,7 +5694,7 @@
         <v>115</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>42</v>
@@ -5614,7 +5728,7 @@
         <v>117</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>42</v>
@@ -5639,7 +5753,7 @@
         <v>6.5625</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="K28" s="15" t="n">
         <v>40</v>
@@ -5650,7 +5764,7 @@
         <v>120</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>42</v>
@@ -5684,7 +5798,7 @@
         <v>123</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>125</v>
@@ -5718,7 +5832,7 @@
         <v>128</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>206</v>
@@ -5742,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="K31" s="15" t="n">
         <v>40</v>
@@ -5750,10 +5864,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>130</v>
@@ -5783,7 +5897,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>130</v>
@@ -5812,7 +5926,7 @@
         <v>35998.381</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="I34" s="29" t="n">
         <f aca="false">SUM(I5:I32)</f>
@@ -5821,7 +5935,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="30" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="F35" s="31" t="n">
         <f aca="false">ROUND(F34,-2)</f>
@@ -5854,12 +5968,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5867,68 +5981,68 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B5" s="28" t="n">
         <f aca="false">'Mano de obra'!$I$34</f>
         <v>83.0787619047619</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B6" s="32" t="n">
         <v>1.35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B7" s="33" t="n">
         <v>0.1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B8" s="34" t="n">
         <f aca="false">ROUNDUP(B5/B6*(1+B7),0)</f>
         <v>68</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B9" s="28" t="n">
         <f aca="false">B8/6</f>
         <v>11.3333333333333</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5937,13 +6051,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="30" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B12" s="34" t="n">
         <f aca="false">B8*Precios!$D$33</f>
@@ -5953,7 +6067,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B13" s="34" t="n">
         <f aca="false">B8*Precios!$D$34</f>
@@ -5963,26 +6077,26 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B14" s="34" t="n">
         <f aca="false">6*Precios!$D$34</f>
         <v>480</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B15" s="34" t="n">
         <f aca="false">14*Precios!$D$31</f>
         <v>2100</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5994,48 +6108,48 @@
         <v>300</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B17" s="34" t="n">
         <f aca="false">Precios!$D$37</f>
         <v>1000</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B18" s="34" t="n">
         <f aca="false">Precios!$D$38</f>
         <v>400</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">Precios!$D$40*Precios!$D$39</f>
         <v>3040</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">Precios!$D$41</f>
@@ -6045,18 +6159,18 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B21" s="35" t="n">
         <v>600</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B22" s="35" t="n">
         <v>400</v>
@@ -6065,18 +6179,18 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B23" s="35" t="n">
         <v>600</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B24" s="36" t="n">
         <f aca="false">SUM(B12:B23)</f>
@@ -6090,43 +6204,43 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B26" s="36" t="n">
         <f aca="false">'Mano de obra'!$F$35</f>
         <v>36000</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B27" s="36" t="n">
         <f aca="false">B26-B24</f>
         <v>11900</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B28" s="34" t="n">
-        <f aca="false">(B17+B18+B19+B20)*Precios!$D$42</f>
+        <f aca="false">(B17+B18+B19+B20)*Precios!$D$44</f>
         <v>2403</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="B29" s="36" t="n">
         <f aca="false">B27+B28</f>
@@ -6136,19 +6250,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B30" s="34" t="n">
         <f aca="false">B29/B9</f>
         <v>1262.02941176471</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B31" s="6" t="n">
         <f aca="false">B29/B26</f>
@@ -6158,18 +6272,18 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6251,49 +6365,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B5" s="28" t="n">
         <v>19.3</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>29.2</v>
@@ -6303,7 +6417,7 @@
         <v>0.660958904109589</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="G5" s="28" t="n">
         <v>22</v>
@@ -6315,13 +6429,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>18.6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="D6" s="28" t="n">
         <v>23.4</v>
@@ -6331,7 +6445,7 @@
         <v>0.794871794871795</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="G6" s="28" t="n">
         <v>22</v>
@@ -6343,39 +6457,39 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="G7" s="28" t="n">
         <v>13.1</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>5.2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="D8" s="28" t="n">
         <v>45.1</v>
@@ -6385,7 +6499,7 @@
         <v>0.11529933481153</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="G8" s="28" t="n">
         <v>30.1</v>
@@ -6397,18 +6511,18 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>37</v>
@@ -6417,16 +6531,16 @@
         <v>142</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="B12" s="25" t="n">
         <v>72</v>
@@ -6447,12 +6561,12 @@
         <v>1360.34</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B13" s="25" t="n">
         <v>22</v>
@@ -6473,12 +6587,12 @@
         <v>1197.02</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B14" s="25" t="n">
         <v>18</v>
@@ -6499,12 +6613,12 @@
         <v>326.46</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="B15" s="25" t="n">
         <v>0</v>
@@ -6525,74 +6639,74 @@
         <v>-395.56</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F16" s="36" t="n">
         <f aca="false">SUM(F12:F15)</f>
         <v>2488.26</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B17" s="28" t="n">
         <f aca="false">511/250</f>
         <v>2.044</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="30" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="F18" s="39" t="n">
         <f aca="false">ROUND(B17/'INT Mi costo y ganancia'!B6*(Precios!$D$33+Precios!$D$34),0)</f>
         <v>318</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -6602,47 +6716,47 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B26" s="41"/>
       <c r="C26" s="4" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B27" s="41"/>
       <c r="C27" s="4" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B28" s="41"/>
       <c r="C28" s="4" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="B29" s="41"/>
       <c r="C29" s="4" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="4" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
